--- a/ns-3.45/result_csv/cu_0119_1st.xlsx
+++ b/ns-3.45/result_csv/cu_0119_1st.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawamasahiro/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3D9D28-C2C1-FB46-A713-A641EFCEAB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47661BC-9A97-2645-9337-D07A53216D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="1080" windowWidth="27900" windowHeight="15920" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
+    <workbookView xWindow="38320" yWindow="4320" windowWidth="27900" windowHeight="15920" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="23">
   <si>
     <t>Stations</t>
   </si>
@@ -102,6 +102,10 @@
   </si>
   <si>
     <t>Auto</t>
+  </si>
+  <si>
+    <t>predict(rxp)</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -219,347 +223,8 @@
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="2"/>
+          <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:v>Radius=10m</c:v>
-          </c:tx>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$15:$I$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>10.106299999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.027000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>29.929099999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40.900199999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>51.194499999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>62.548999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>72.8172</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>81.631100000000004</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>85.874099999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>90.224500000000006</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.726399999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>89.557299999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.909599999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001A-9316-0C4A-8562-37F50A4D592D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Radius=5m</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$2:$I$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>9.1286100000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>18.0457</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>27.614000000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>38.2883</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>47.786099999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>57.730400000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>70.084500000000006</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>77.872699999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>83.590400000000002</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>88.548299999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.776300000000006</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.846500000000006</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>90.504400000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001B-9316-0C4A-8562-37F50A4D592D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>Radius=15m</c:v>
-          </c:tx>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$I$28:$I$40</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>9.85351</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>19.834900000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>29.875800000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>42.8964</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>52.767699999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>62.839599999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>72.9298</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>80.255600000000001</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>86.286199999999994</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>85.724000000000004</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>85.069900000000004</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>86.011600000000001</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>86.267099999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000017-9316-0C4A-8562-37F50A4D592D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>Radius=20m</c:v>
-          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -634,48 +299,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$41:$I$53</c:f>
+              <c:f>Sheet1!$I$2:$I$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>11.155099999999999</c:v>
+                  <c:v>9.1286100000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.5413</c:v>
+                  <c:v>18.0457</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34.300400000000003</c:v>
+                  <c:v>27.614000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.510100000000001</c:v>
+                  <c:v>38.2883</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.146999999999998</c:v>
+                  <c:v>47.786099999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>66.2089</c:v>
+                  <c:v>57.730400000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>77.522599999999997</c:v>
+                  <c:v>70.084500000000006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>83.988500000000002</c:v>
+                  <c:v>77.872699999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.121899999999997</c:v>
+                  <c:v>83.590400000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>87.564400000000006</c:v>
+                  <c:v>88.548299999999998</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.620800000000003</c:v>
+                  <c:v>89.776300000000006</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>87.615200000000002</c:v>
+                  <c:v>90.846500000000006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87.388999999999996</c:v>
+                  <c:v>90.504400000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -683,16 +348,37 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000019-9316-0C4A-8562-37F50A4D592D}"/>
+              <c16:uniqueId val="{00000000-7017-7643-9F6C-C63D46C45D77}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>Radius=25m</c:v>
-          </c:tx>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$A$2:$A$14</c:f>
@@ -743,48 +429,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$54:$I$66</c:f>
+              <c:f>Sheet1!$U$2:$U$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>11.378500000000001</c:v>
+                  <c:v>2.568954730516539</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.463000000000001</c:v>
+                  <c:v>17.526793641561394</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34.715699999999998</c:v>
+                  <c:v>29.885187591896635</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.491399999999999</c:v>
+                  <c:v>40.09588058972718</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.714399999999998</c:v>
+                  <c:v>48.532110403643827</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.334000000000003</c:v>
+                  <c:v>61.261088521224956</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>79.526300000000006</c:v>
+                  <c:v>73.198278059855596</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>86.979299999999995</c:v>
+                  <c:v>82.694866040660486</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>87.809299999999993</c:v>
+                  <c:v>86.351096085559902</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>89.042900000000003</c:v>
+                  <c:v>87.758761466878511</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>88.526799999999994</c:v>
+                  <c:v>88.300719112165922</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>89.659300000000002</c:v>
+                  <c:v>88.509375297921068</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>87.439599999999999</c:v>
+                  <c:v>88.58970888899124</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -792,7 +478,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000001D-9316-0C4A-8562-37F50A4D592D}"/>
+              <c16:uniqueId val="{00000001-7017-7643-9F6C-C63D46C45D77}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -804,11 +490,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="854057727"/>
-        <c:axId val="853482495"/>
+        <c:axId val="555403903"/>
+        <c:axId val="476270079"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="854057727"/>
+        <c:axId val="555403903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -828,25 +514,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>station</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -884,12 +551,12 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="853482495"/>
+        <c:crossAx val="476270079"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="853482495"/>
+        <c:axId val="476270079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -909,25 +576,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>Utilization</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -965,20 +613,44 @@
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="854057727"/>
+        <c:crossAx val="555403903"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -997,27 +669,1636 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$15:$V$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>10.106299999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.027000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29.929099999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40.900199999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51.194499999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>62.548999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>72.8172</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>81.631100000000004</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85.874099999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>90.224500000000006</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>89.726399999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>89.557299999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>89.909599999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-208C-1446-9A8F-635704912895}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$15:$U$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="13"/>
+                <c:pt idx="0">
+                  <c:v>7.4083537639594885</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.849113565543391</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33.780288893174493</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43.638007368836654</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51.782604265369315</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>64.071552997119383</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75.596084572737468</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>84.7643840029546</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>88.29422144616575</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>89.653225094588308</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>90.176447748928339</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>90.377890877011481</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>90.455447407707013</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-208C-1446-9A8F-635704912895}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="555403903"/>
+        <c:axId val="476270079"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="555403903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="476270079"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="476270079"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="555403903"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>733426</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>12220</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>940092</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>168458</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>123440</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>7986</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>767839</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>181888</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="グラフ 4">
+        <xdr:cNvPr id="4" name="グラフ 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F042B5A8-D3C3-8EF6-5DD8-185B1B8DE2D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72CE6E12-6547-AA90-B4E9-071A3082BF32}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1030,6 +2311,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>919655</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>29195</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>747403</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>42625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="グラフ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFBE54A7-0B56-6642-B7ED-4C22AEC96B24}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1355,10 +2674,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DCF3BA-54BF-0749-8B62-B90EA21C5515}">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:W66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1419,8 +2738,14 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1481,8 +2806,15 @@
       <c r="T2">
         <v>35.314999999999998</v>
       </c>
+      <c r="U2">
+        <f>88.64*(1-EXP(-(-0.0052*$C2 - 0.0062*$S2 + 0.2169*$A2 - 0.4879)))</f>
+        <v>2.568954730516539</v>
+      </c>
+      <c r="V2">
+        <v>9.1286100000000001</v>
+      </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1543,8 +2875,19 @@
       <c r="T3">
         <v>35.318199999999997</v>
       </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U14" si="0">88.64*(1-EXP(-(-0.0052*$C3 - 0.0062*$S3 + 0.2169*$A3 - 0.4879)))</f>
+        <v>17.526793641561394</v>
+      </c>
+      <c r="V3">
+        <v>18.0457</v>
+      </c>
+      <c r="W3">
+        <f t="shared" ref="W3:W14" si="1">100*(1-EXP(-(6.207*$C3 - 0.0057*$S3 + 30.9139*$A3 - 0.3386)))</f>
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1605,8 +2948,19 @@
       <c r="T4">
         <v>35.317799999999998</v>
       </c>
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>29.885187591896635</v>
+      </c>
+      <c r="V4">
+        <v>27.614000000000001</v>
+      </c>
+      <c r="W4">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1667,8 +3021,19 @@
       <c r="T5">
         <v>35.323399999999999</v>
       </c>
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>40.09588058972718</v>
+      </c>
+      <c r="V5">
+        <v>38.2883</v>
+      </c>
+      <c r="W5">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1729,8 +3094,19 @@
       <c r="T6">
         <v>35.355600000000003</v>
       </c>
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>48.532110403643827</v>
+      </c>
+      <c r="V6">
+        <v>47.786099999999998</v>
+      </c>
+      <c r="W6">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>7</v>
       </c>
@@ -1791,8 +3167,19 @@
       <c r="T7">
         <v>35.722299999999997</v>
       </c>
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>61.261088521224956</v>
+      </c>
+      <c r="V7">
+        <v>57.730400000000003</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>10</v>
       </c>
@@ -1853,8 +3240,19 @@
       <c r="T8">
         <v>36.133499999999998</v>
       </c>
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>73.198278059855596</v>
+      </c>
+      <c r="V8">
+        <v>70.084500000000006</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>15</v>
       </c>
@@ -1915,8 +3313,19 @@
       <c r="T9">
         <v>36.632300000000001</v>
       </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>82.694866040660486</v>
+      </c>
+      <c r="V9">
+        <v>77.872699999999995</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>20</v>
       </c>
@@ -1977,8 +3386,19 @@
       <c r="T10">
         <v>36.738900000000001</v>
       </c>
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>86.351096085559902</v>
+      </c>
+      <c r="V10">
+        <v>83.590400000000002</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>25</v>
       </c>
@@ -2039,8 +3459,19 @@
       <c r="T11">
         <v>36.990600000000001</v>
       </c>
+      <c r="U11">
+        <f t="shared" si="0"/>
+        <v>87.758761466878511</v>
+      </c>
+      <c r="V11">
+        <v>88.548299999999998</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>30</v>
       </c>
@@ -2101,8 +3532,19 @@
       <c r="T12">
         <v>36.9422</v>
       </c>
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>88.300719112165922</v>
+      </c>
+      <c r="V12">
+        <v>89.776300000000006</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>35</v>
       </c>
@@ -2163,8 +3605,19 @@
       <c r="T13">
         <v>37.158700000000003</v>
       </c>
+      <c r="U13">
+        <f t="shared" si="0"/>
+        <v>88.509375297921068</v>
+      </c>
+      <c r="V13">
+        <v>90.846500000000006</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:23">
       <c r="A14">
         <v>40</v>
       </c>
@@ -2225,8 +3678,19 @@
       <c r="T14">
         <v>37.303800000000003</v>
       </c>
+      <c r="U14">
+        <f t="shared" si="0"/>
+        <v>88.58970888899124</v>
+      </c>
+      <c r="V14">
+        <v>90.504400000000004</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:23">
       <c r="A15">
         <v>1</v>
       </c>
@@ -2287,8 +3751,15 @@
       <c r="T15">
         <v>26.302199999999999</v>
       </c>
+      <c r="U15">
+        <f t="shared" ref="U3:U66" si="2">90.504*(1-EXP(-(-0.0052*$C15 - 0.0062*$S15 + 0.2169*$A15 - 0.4879)))</f>
+        <v>7.4083537639594885</v>
+      </c>
+      <c r="V15">
+        <v>10.106299999999999</v>
+      </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:23">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2349,8 +3820,15 @@
       <c r="T16">
         <v>26.3062</v>
       </c>
+      <c r="U16">
+        <f t="shared" si="2"/>
+        <v>21.849113565543391</v>
+      </c>
+      <c r="V16">
+        <v>20.027000000000001</v>
+      </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:22">
       <c r="A17">
         <v>3</v>
       </c>
@@ -2411,8 +3889,15 @@
       <c r="T17">
         <v>26.305</v>
       </c>
+      <c r="U17">
+        <f t="shared" si="2"/>
+        <v>33.780288893174493</v>
+      </c>
+      <c r="V17">
+        <v>29.929099999999998</v>
+      </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:22">
       <c r="A18">
         <v>4</v>
       </c>
@@ -2473,8 +3958,15 @@
       <c r="T18">
         <v>26.320499999999999</v>
       </c>
+      <c r="U18">
+        <f t="shared" si="2"/>
+        <v>43.638007368836654</v>
+      </c>
+      <c r="V18">
+        <v>40.900199999999998</v>
+      </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:22">
       <c r="A19">
         <v>5</v>
       </c>
@@ -2535,8 +4027,15 @@
       <c r="T19">
         <v>26.374199999999998</v>
       </c>
+      <c r="U19">
+        <f t="shared" si="2"/>
+        <v>51.782604265369315</v>
+      </c>
+      <c r="V19">
+        <v>51.194499999999998</v>
+      </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:22">
       <c r="A20">
         <v>7</v>
       </c>
@@ -2597,8 +4096,15 @@
       <c r="T20">
         <v>26.841999999999999</v>
       </c>
+      <c r="U20">
+        <f t="shared" si="2"/>
+        <v>64.071552997119383</v>
+      </c>
+      <c r="V20">
+        <v>62.548999999999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:22">
       <c r="A21">
         <v>10</v>
       </c>
@@ -2659,8 +4165,15 @@
       <c r="T21">
         <v>27.1402</v>
       </c>
+      <c r="U21">
+        <f t="shared" si="2"/>
+        <v>75.596084572737468</v>
+      </c>
+      <c r="V21">
+        <v>72.8172</v>
+      </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:22">
       <c r="A22">
         <v>15</v>
       </c>
@@ -2721,8 +4234,15 @@
       <c r="T22">
         <v>27.639199999999999</v>
       </c>
+      <c r="U22">
+        <f t="shared" si="2"/>
+        <v>84.7643840029546</v>
+      </c>
+      <c r="V22">
+        <v>81.631100000000004</v>
+      </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:22">
       <c r="A23">
         <v>20</v>
       </c>
@@ -2783,8 +4303,15 @@
       <c r="T23">
         <v>28.081099999999999</v>
       </c>
+      <c r="U23">
+        <f t="shared" si="2"/>
+        <v>88.29422144616575</v>
+      </c>
+      <c r="V23">
+        <v>85.874099999999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:22">
       <c r="A24">
         <v>25</v>
       </c>
@@ -2845,8 +4372,15 @@
       <c r="T24">
         <v>28.207899999999999</v>
       </c>
+      <c r="U24">
+        <f t="shared" si="2"/>
+        <v>89.653225094588308</v>
+      </c>
+      <c r="V24">
+        <v>90.224500000000006</v>
+      </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:22">
       <c r="A25">
         <v>30</v>
       </c>
@@ -2907,8 +4441,15 @@
       <c r="T25">
         <v>28.1159</v>
       </c>
+      <c r="U25">
+        <f t="shared" si="2"/>
+        <v>90.176447748928339</v>
+      </c>
+      <c r="V25">
+        <v>89.726399999999998</v>
+      </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:22">
       <c r="A26">
         <v>35</v>
       </c>
@@ -2969,8 +4510,15 @@
       <c r="T26">
         <v>27.9954</v>
       </c>
+      <c r="U26">
+        <f t="shared" si="2"/>
+        <v>90.377890877011481</v>
+      </c>
+      <c r="V26">
+        <v>89.557299999999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:22">
       <c r="A27">
         <v>40</v>
       </c>
@@ -3031,8 +4579,15 @@
       <c r="T27">
         <v>28.028300000000002</v>
       </c>
+      <c r="U27">
+        <f t="shared" si="2"/>
+        <v>90.455447407707013</v>
+      </c>
+      <c r="V27">
+        <v>89.909599999999998</v>
+      </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:22">
       <c r="A28">
         <v>1</v>
       </c>
@@ -3093,8 +4648,15 @@
       <c r="T28">
         <v>21.043800000000001</v>
       </c>
+      <c r="U28">
+        <f t="shared" si="2"/>
+        <v>10.085876405500846</v>
+      </c>
+      <c r="V28">
+        <v>9.85351</v>
+      </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:22">
       <c r="A29">
         <v>2</v>
       </c>
@@ -3155,8 +4717,15 @@
       <c r="T29">
         <v>21.0504</v>
       </c>
+      <c r="U29">
+        <f t="shared" si="2"/>
+        <v>24.061323485164653</v>
+      </c>
+      <c r="V29">
+        <v>19.834900000000001</v>
+      </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:22">
       <c r="A30">
         <v>3</v>
       </c>
@@ -3217,8 +4786,15 @@
       <c r="T30">
         <v>21.048100000000002</v>
       </c>
+      <c r="U30">
+        <f t="shared" si="2"/>
+        <v>35.608050366613789</v>
+      </c>
+      <c r="V30">
+        <v>29.875800000000002</v>
+      </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:22">
       <c r="A31">
         <v>4</v>
       </c>
@@ -3279,8 +4855,15 @@
       <c r="T31">
         <v>21.1</v>
       </c>
+      <c r="U31">
+        <f t="shared" si="2"/>
+        <v>45.14813169029388</v>
+      </c>
+      <c r="V31">
+        <v>42.8964</v>
+      </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:22">
       <c r="A32">
         <v>5</v>
       </c>
@@ -3341,8 +4924,15 @@
       <c r="T32">
         <v>21.193200000000001</v>
       </c>
+      <c r="U32">
+        <f t="shared" si="2"/>
+        <v>53.030291942014273</v>
+      </c>
+      <c r="V32">
+        <v>52.767699999999998</v>
+      </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:22">
       <c r="A33">
         <v>7</v>
       </c>
@@ -3403,8 +4993,15 @@
       <c r="T33">
         <v>21.593900000000001</v>
       </c>
+      <c r="U33">
+        <f t="shared" si="2"/>
+        <v>64.923263989540303</v>
+      </c>
+      <c r="V33">
+        <v>62.839599999999997</v>
+      </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:22">
       <c r="A34">
         <v>10</v>
       </c>
@@ -3465,8 +5062,15 @@
       <c r="T34">
         <v>21.9316</v>
       </c>
+      <c r="U34">
+        <f t="shared" si="2"/>
+        <v>76.076450066030503</v>
+      </c>
+      <c r="V34">
+        <v>72.9298</v>
+      </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:22">
       <c r="A35">
         <v>15</v>
       </c>
@@ -3527,8 +5131,15 @@
       <c r="T35">
         <v>22.360299999999999</v>
       </c>
+      <c r="U35">
+        <f t="shared" si="2"/>
+        <v>84.949326926945915</v>
+      </c>
+      <c r="V35">
+        <v>80.255600000000001</v>
+      </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:22">
       <c r="A36">
         <v>20</v>
       </c>
@@ -3589,8 +5200,15 @@
       <c r="T36">
         <v>22.439</v>
       </c>
+      <c r="U36">
+        <f t="shared" si="2"/>
+        <v>88.365425322405869</v>
+      </c>
+      <c r="V36">
+        <v>86.286199999999994</v>
+      </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:22">
       <c r="A37">
         <v>25</v>
       </c>
@@ -3651,8 +5269,15 @@
       <c r="T37">
         <v>22.544599999999999</v>
       </c>
+      <c r="U37">
+        <f t="shared" si="2"/>
+        <v>89.680638914388496</v>
+      </c>
+      <c r="V37">
+        <v>85.724000000000004</v>
+      </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:22">
       <c r="A38">
         <v>30</v>
       </c>
@@ -3713,8 +5338,15 @@
       <c r="T38">
         <v>22.780899999999999</v>
       </c>
+      <c r="U38">
+        <f t="shared" si="2"/>
+        <v>90.187002195620295</v>
+      </c>
+      <c r="V38">
+        <v>85.069900000000004</v>
+      </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:22">
       <c r="A39">
         <v>35</v>
       </c>
@@ -3775,8 +5407,15 @@
       <c r="T39">
         <v>23.2805</v>
       </c>
+      <c r="U39">
+        <f t="shared" si="2"/>
+        <v>90.381954387524985</v>
+      </c>
+      <c r="V39">
+        <v>86.011600000000001</v>
+      </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:22">
       <c r="A40">
         <v>40</v>
       </c>
@@ -3837,8 +5476,15 @@
       <c r="T40">
         <v>22.877800000000001</v>
       </c>
+      <c r="U40">
+        <f t="shared" si="2"/>
+        <v>90.457011877941724</v>
+      </c>
+      <c r="V40">
+        <v>86.267099999999999</v>
+      </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:22">
       <c r="A41">
         <v>1</v>
       </c>
@@ -3899,8 +5545,15 @@
       <c r="T41">
         <v>17.3354</v>
       </c>
+      <c r="U41">
+        <f t="shared" si="2"/>
+        <v>11.933152897972789</v>
+      </c>
+      <c r="V41">
+        <v>11.155099999999999</v>
+      </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:22">
       <c r="A42">
         <v>2</v>
       </c>
@@ -3961,8 +5614,15 @@
       <c r="T42">
         <v>17.332599999999999</v>
       </c>
+      <c r="U42">
+        <f t="shared" si="2"/>
+        <v>25.587571412083058</v>
+      </c>
+      <c r="V42">
+        <v>22.5413</v>
+      </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:22">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4023,8 +5683,15 @@
       <c r="T43">
         <v>17.330200000000001</v>
       </c>
+      <c r="U43">
+        <f t="shared" si="2"/>
+        <v>36.869059611258926</v>
+      </c>
+      <c r="V43">
+        <v>34.300400000000003</v>
+      </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:22">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4085,8 +5752,15 @@
       <c r="T44">
         <v>17.366599999999998</v>
       </c>
+      <c r="U44">
+        <f t="shared" si="2"/>
+        <v>46.189996702547219</v>
+      </c>
+      <c r="V44">
+        <v>46.510100000000001</v>
+      </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:22">
       <c r="A45">
         <v>5</v>
       </c>
@@ -4147,8 +5821,15 @@
       <c r="T45">
         <v>17.549299999999999</v>
       </c>
+      <c r="U45">
+        <f t="shared" si="2"/>
+        <v>53.891096657258927</v>
+      </c>
+      <c r="V45">
+        <v>55.146999999999998</v>
+      </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:22">
       <c r="A46">
         <v>7</v>
       </c>
@@ -4209,8 +5890,15 @@
       <c r="T46">
         <v>18.141100000000002</v>
       </c>
+      <c r="U46">
+        <f t="shared" si="2"/>
+        <v>65.510876460213325</v>
+      </c>
+      <c r="V46">
+        <v>66.2089</v>
+      </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:22">
       <c r="A47">
         <v>10</v>
       </c>
@@ -4271,8 +5959,15 @@
       <c r="T47">
         <v>18.357700000000001</v>
       </c>
+      <c r="U47">
+        <f t="shared" si="2"/>
+        <v>76.407863840012297</v>
+      </c>
+      <c r="V47">
+        <v>77.522599999999997</v>
+      </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:22">
       <c r="A48">
         <v>15</v>
       </c>
@@ -4333,8 +6028,15 @@
       <c r="T48">
         <v>18.4998</v>
       </c>
+      <c r="U48">
+        <f t="shared" si="2"/>
+        <v>85.076922754012969</v>
+      </c>
+      <c r="V48">
+        <v>83.988500000000002</v>
+      </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:22">
       <c r="A49">
         <v>20</v>
       </c>
@@ -4395,8 +6097,15 @@
       <c r="T49">
         <v>19.085899999999999</v>
       </c>
+      <c r="U49">
+        <f t="shared" si="2"/>
+        <v>88.414550302606045</v>
+      </c>
+      <c r="V49">
+        <v>88.121899999999997</v>
+      </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:22">
       <c r="A50">
         <v>25</v>
       </c>
@@ -4457,8 +6166,15 @@
       <c r="T50">
         <v>19.157499999999999</v>
       </c>
+      <c r="U50">
+        <f t="shared" si="2"/>
+        <v>89.69955225767832</v>
+      </c>
+      <c r="V50">
+        <v>87.564400000000006</v>
+      </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:22">
       <c r="A51">
         <v>30</v>
       </c>
@@ -4519,8 +6235,15 @@
       <c r="T51">
         <v>19.297599999999999</v>
       </c>
+      <c r="U51">
+        <f t="shared" si="2"/>
+        <v>90.194283919764331</v>
+      </c>
+      <c r="V51">
+        <v>87.620800000000003</v>
+      </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:22">
       <c r="A52">
         <v>35</v>
       </c>
@@ -4581,8 +6304,15 @@
       <c r="T52">
         <v>19.629200000000001</v>
       </c>
+      <c r="U52">
+        <f t="shared" si="2"/>
+        <v>90.384757884807158</v>
+      </c>
+      <c r="V52">
+        <v>87.615200000000002</v>
+      </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:22">
       <c r="A53">
         <v>40</v>
       </c>
@@ -4643,8 +6373,15 @@
       <c r="T53">
         <v>19.109400000000001</v>
       </c>
+      <c r="U53">
+        <f t="shared" si="2"/>
+        <v>90.458091237287888</v>
+      </c>
+      <c r="V53">
+        <v>87.388999999999996</v>
+      </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:22">
       <c r="A54">
         <v>1</v>
       </c>
@@ -4705,8 +6442,15 @@
       <c r="T54">
         <v>14.430999999999999</v>
       </c>
+      <c r="U54">
+        <f t="shared" si="2"/>
+        <v>13.336724966993261</v>
+      </c>
+      <c r="V54">
+        <v>11.378500000000001</v>
+      </c>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:22">
       <c r="A55">
         <v>2</v>
       </c>
@@ -4767,8 +6511,15 @@
       <c r="T55">
         <v>14.479799999999999</v>
       </c>
+      <c r="U55">
+        <f t="shared" si="2"/>
+        <v>26.74722399758015</v>
+      </c>
+      <c r="V55">
+        <v>22.463000000000001</v>
+      </c>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:22">
       <c r="A56">
         <v>3</v>
       </c>
@@ -4829,8 +6580,15 @@
       <c r="T56">
         <v>14.4993</v>
       </c>
+      <c r="U56">
+        <f t="shared" si="2"/>
+        <v>37.827182210541331</v>
+      </c>
+      <c r="V56">
+        <v>34.715699999999998</v>
+      </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:22">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4891,8 +6649,15 @@
       <c r="T57">
         <v>14.500400000000001</v>
       </c>
+      <c r="U57">
+        <f t="shared" si="2"/>
+        <v>46.981612162846631</v>
+      </c>
+      <c r="V57">
+        <v>55.491399999999999</v>
+      </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:22">
       <c r="A58">
         <v>5</v>
       </c>
@@ -4953,8 +6718,15 @@
       <c r="T58">
         <v>14.805899999999999</v>
       </c>
+      <c r="U58">
+        <f t="shared" si="2"/>
+        <v>54.545141387499491</v>
+      </c>
+      <c r="V58">
+        <v>61.714399999999998</v>
+      </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:22">
       <c r="A59">
         <v>7</v>
       </c>
@@ -5015,8 +6787,15 @@
       <c r="T59">
         <v>14.797000000000001</v>
       </c>
+      <c r="U59">
+        <f t="shared" si="2"/>
+        <v>65.95734803856439</v>
+      </c>
+      <c r="V59">
+        <v>67.334000000000003</v>
+      </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:22">
       <c r="A60">
         <v>10</v>
       </c>
@@ -5077,8 +6856,15 @@
       <c r="T60">
         <v>15.4857</v>
       </c>
+      <c r="U60">
+        <f t="shared" si="2"/>
+        <v>76.659674068933171</v>
+      </c>
+      <c r="V60">
+        <v>79.526300000000006</v>
+      </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:22">
       <c r="A61">
         <v>15</v>
       </c>
@@ -5139,8 +6925,15 @@
       <c r="T61">
         <v>15.864800000000001</v>
       </c>
+      <c r="U61">
+        <f t="shared" si="2"/>
+        <v>85.17387085015595</v>
+      </c>
+      <c r="V61">
+        <v>86.979299999999995</v>
+      </c>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:22">
       <c r="A62">
         <v>20</v>
       </c>
@@ -5201,8 +6994,15 @@
       <c r="T62">
         <v>15.8827</v>
       </c>
+      <c r="U62">
+        <f t="shared" si="2"/>
+        <v>88.451875765459675</v>
+      </c>
+      <c r="V62">
+        <v>87.809299999999993</v>
+      </c>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="1:22">
       <c r="A63">
         <v>25</v>
       </c>
@@ -5263,8 +7063,15 @@
       <c r="T63">
         <v>16.226299999999998</v>
       </c>
+      <c r="U63">
+        <f t="shared" si="2"/>
+        <v>89.713922732526868</v>
+      </c>
+      <c r="V63">
+        <v>89.042900000000003</v>
+      </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:22">
       <c r="A64">
         <v>30</v>
       </c>
@@ -5325,8 +7132,15 @@
       <c r="T64">
         <v>16.788599999999999</v>
       </c>
+      <c r="U64">
+        <f t="shared" si="2"/>
+        <v>90.199816618667029</v>
+      </c>
+      <c r="V64">
+        <v>88.526799999999994</v>
+      </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:22">
       <c r="A65">
         <v>35</v>
       </c>
@@ -5387,8 +7201,15 @@
       <c r="T65">
         <v>16.3247</v>
       </c>
+      <c r="U65">
+        <f t="shared" si="2"/>
+        <v>90.38688799932811</v>
+      </c>
+      <c r="V65">
+        <v>89.659300000000002</v>
+      </c>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="1:22">
       <c r="A66">
         <v>40</v>
       </c>
@@ -5448,6 +7269,13 @@
       </c>
       <c r="T66">
         <v>15.8339</v>
+      </c>
+      <c r="U66">
+        <f t="shared" si="2"/>
+        <v>90.4589113411743</v>
+      </c>
+      <c r="V66">
+        <v>87.439599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ns-3.45/result_csv/cu_0119_1st.xlsx
+++ b/ns-3.45/result_csv/cu_0119_1st.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47661BC-9A97-2645-9337-D07A53216D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD218369-6AF1-B44A-81EC-D8514EBBD755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38320" yWindow="4320" windowWidth="27900" windowHeight="15920" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
+    <workbookView xWindow="39680" yWindow="820" windowWidth="38400" windowHeight="21000" xr2:uid="{D901B013-2279-A942-9DB6-FAF328F9E094}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -186,45 +186,1015 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.676902631295586E-2"/>
+          <c:y val="0.31797821200980209"/>
+          <c:w val="0.89339176271235099"/>
+          <c:h val="0.47246051199199784"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="smoothMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="8"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>predict(station=1)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$2:$S$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$2:$V$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.1286100000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.106299999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.85351</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.155099999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.378500000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000028-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>measured(station=1)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$2:$S$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$2:$U$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.360015708982826</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.022571347333332</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6322726813498107</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.433148794365955</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.801684339618824</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000029-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>predict(station=10)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$62:$S$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$62:$U$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>88.58970888899124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.592447385962487</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88.593979634720611</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.59503676382478</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88.595839977036249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002A-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>measured(station=10)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$32:$S$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$32:$V$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>70.084500000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72.8172</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.9298</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77.522599999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.526300000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002B-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>predict(station=20)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$42:$S$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$42:$U$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>86.344372406534674</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>86.468166914490936</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.537456531090911</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86.585271203899808</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>86.62160689565043</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002C-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="13"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>measured(station=20)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$42:$S$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$42:$V$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>83.590400000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.874099999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.286199999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.121899999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87.809299999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002D-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="14"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>predict(station=30)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$32:$S$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$32:$U$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>73.168421684466864</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>74.004283240917346</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>74.472127313592807</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74.794972385599863</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75.040311281184088</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002E-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="15"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>measured(station=30)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$62:$S$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$62:$V$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>90.504400000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.909599999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.267099999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.388999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87.439599999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002F-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>predict(station=2)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$7:$S$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$7:$V$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>18.0457</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.027000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.834900000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.5413</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22.463000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000019-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>measured(station=2)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$7:$S$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$7:$U$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17.359290834494285</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.211241622123296</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23.367235435120978</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.855021683696215</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.985631585286583</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001B-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>predict(station=10)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$62:$S$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$62:$U$66</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>88.58970888899124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>88.592447385962487</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88.593979634720611</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.59503676382478</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88.595839977036249</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001D-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="11"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$22:$S$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$22:$V$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>47.786099999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>51.194499999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.767699999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55.146999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61.714399999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000001F-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:v>predict(station=20)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$42:$S$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$42:$U$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>86.344372406534674</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>86.468166914490936</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.537456531090911</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86.585271203899808</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>86.62160689565043</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000021-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="13"/>
+          <c:tx>
+            <c:v>measured(station=20)</c:v>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$42:$S$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$V$42:$V$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>83.590400000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.874099999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>86.286199999999994</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>88.121899999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>87.809299999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000023-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="14"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$S$22:$S$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$U$22:$U$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>48.445606052324024</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.617561127108793</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>51.833236498243849</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.672137374954424</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.309641343397544</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000025-6829-0C45-BF0A-6153B0514DED}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="15"/>
+          <c:tx>
+            <c:v>measured(station=30)</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -251,96 +1221,48 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
+              <c:f>Sheet1!$S$62:$S$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>-52.646799999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>-61.677700000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>-66.960400000000007</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>-70.708600000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
+                  <c:v>-73.615899999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$I$2:$I$14</c:f>
+              <c:f>Sheet1!$V$62:$V$66</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>9.1286100000000001</c:v>
+                  <c:v>90.504400000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.0457</c:v>
+                  <c:v>89.909599999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27.614000000000001</c:v>
+                  <c:v>86.267099999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.2883</c:v>
+                  <c:v>87.388999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47.786099999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>57.730400000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>70.084500000000006</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>77.872699999999995</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>83.590400000000002</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>88.548299999999998</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.776300000000006</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.846500000000006</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>90.504400000000004</c:v>
+                  <c:v>87.439599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -348,137 +1270,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7017-7643-9F6C-C63D46C45D77}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$U$2:$U$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>2.568954730516539</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>17.526793641561394</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>29.885187591896635</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40.09588058972718</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>48.532110403643827</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>61.261088521224956</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>73.198278059855596</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>82.694866040660486</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>86.351096085559902</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>87.758761466878511</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>88.300719112165922</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>88.509375297921068</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>88.58970888899124</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7017-7643-9F6C-C63D46C45D77}"/>
+              <c16:uniqueId val="{00000027-6829-0C45-BF0A-6153B0514DED}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -497,6 +1289,7 @@
         <c:axId val="555403903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="-50"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -514,6 +1307,31 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>接続台数</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -532,21 +1350,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -576,6 +1384,36 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>/%</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -594,21 +1432,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="ja-JP"/>
           </a:p>
@@ -617,6 +1445,10 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -624,39 +1456,28 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-    </c:plotArea>
+      <c:txPr>
+        <a:bodyPr rot="0" vert="horz"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:extLst/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="2800"/>
       </a:pPr>
       <a:endParaRPr lang="ja-JP"/>
     </a:p>
@@ -669,1629 +1490,20 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ja-JP"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$V$15:$V$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>10.106299999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>20.027000000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>29.929099999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>40.900199999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>51.194499999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>62.548999999999999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>72.8172</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>81.631100000000004</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>85.874099999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>90.224500000000006</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>89.726399999999998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>89.557299999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>89.909599999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-208C-1446-9A8F-635704912895}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$A$2:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>15</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>25</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$U$15:$U$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
-                <c:pt idx="0">
-                  <c:v>7.4083537639594885</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>21.849113565543391</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>33.780288893174493</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>43.638007368836654</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>51.782604265369315</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>64.071552997119383</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>75.596084572737468</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>84.7643840029546</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>88.29422144616575</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>89.653225094588308</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>90.176447748928339</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>90.377890877011481</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>90.455447407707013</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-208C-1446-9A8F-635704912895}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="555403903"/>
-        <c:axId val="476270079"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="555403903"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="476270079"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="476270079"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="555403903"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>940092</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>168458</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>897466</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>767839</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>181888</xdr:rowOff>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>304797</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>220134</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2311,44 +1523,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>919655</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>29195</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>747403</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>42625</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="グラフ 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFBE54A7-0B56-6642-B7ED-4C22AEC96B24}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2807,8 +1981,8 @@
         <v>35.314999999999998</v>
       </c>
       <c r="U2">
-        <f>88.64*(1-EXP(-(-0.0052*$C2 - 0.0062*$S2 + 0.2169*$A2 - 0.4879)))</f>
-        <v>2.568954730516539</v>
+        <f>88.635042*(1-EXP(-(-0.005187*C2-0.006152*S2+0.216919*A2-0.48788)))</f>
+        <v>2.360015708982826</v>
       </c>
       <c r="V2">
         <v>9.1286100000000001</v>
@@ -2816,13 +1990,13 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
         <v>5</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
       </c>
       <c r="D3">
         <v>1400</v>
@@ -2840,62 +2014,58 @@
         <v>65535</v>
       </c>
       <c r="I3">
-        <v>18.0457</v>
+        <v>10.106299999999999</v>
       </c>
       <c r="J3">
-        <v>10.7767</v>
+        <v>5.3879400000000004</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>7.7002099999999999E-3</v>
       </c>
       <c r="L3">
-        <v>7.3201500000000003E-2</v>
+        <v>9.1091199999999997E-2</v>
       </c>
       <c r="M3">
-        <v>0.137549</v>
+        <v>4.7833899999999998</v>
       </c>
       <c r="N3">
-        <v>161</v>
+        <v>2936</v>
       </c>
       <c r="O3">
-        <v>116888</v>
+        <v>58443</v>
       </c>
       <c r="P3">
-        <v>0.137739</v>
+        <v>5.0236999999999998</v>
       </c>
       <c r="Q3">
         <v>15</v>
       </c>
       <c r="R3">
-        <v>1.19211</v>
+        <v>1.14802</v>
       </c>
       <c r="S3">
-        <v>-52.646799999999999</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T3">
-        <v>35.318199999999997</v>
+        <v>26.302199999999999</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U14" si="0">88.64*(1-EXP(-(-0.0052*$C3 - 0.0062*$S3 + 0.2169*$A3 - 0.4879)))</f>
-        <v>17.526793641561394</v>
+        <f t="shared" ref="U3:U56" si="0">88.635042*(1-EXP(-(-0.005187*C3-0.006152*S3+0.216919*A3-0.48788)))</f>
+        <v>7.022571347333332</v>
       </c>
       <c r="V3">
-        <v>18.0457</v>
-      </c>
-      <c r="W3">
-        <f t="shared" ref="W3:W14" si="1">100*(1-EXP(-(6.207*$C3 - 0.0057*$S3 + 30.9139*$A3 - 0.3386)))</f>
-        <v>100</v>
+        <v>10.106299999999999</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
         <v>5</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
       </c>
       <c r="D4">
         <v>1400</v>
@@ -2913,62 +2083,58 @@
         <v>65535</v>
       </c>
       <c r="I4">
-        <v>27.614000000000001</v>
+        <v>9.85351</v>
       </c>
       <c r="J4">
-        <v>16.161999999999999</v>
+        <v>5.2057900000000004</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>7.9774500000000005E-3</v>
       </c>
       <c r="L4">
-        <v>0.13838800000000001</v>
+        <v>0.100671</v>
       </c>
       <c r="M4">
-        <v>5.20845</v>
+        <v>6.3311500000000001</v>
       </c>
       <c r="N4">
-        <v>9631</v>
+        <v>3813</v>
       </c>
       <c r="O4">
-        <v>175280</v>
+        <v>56413</v>
       </c>
       <c r="P4">
-        <v>5.4946400000000004</v>
+        <v>6.75908</v>
       </c>
       <c r="Q4">
         <v>15</v>
       </c>
       <c r="R4">
-        <v>1.1623699999999999</v>
+        <v>1.1375900000000001</v>
       </c>
       <c r="S4">
-        <v>-52.646799999999999</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T4">
-        <v>35.317799999999998</v>
+        <v>21.043800000000001</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>29.885187591896635</v>
+        <v>9.6322726813498107</v>
       </c>
       <c r="V4">
-        <v>27.614000000000001</v>
-      </c>
-      <c r="W4">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>9.85351</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5">
         <v>5</v>
-      </c>
-      <c r="C5">
-        <v>20</v>
       </c>
       <c r="D5">
         <v>1400</v>
@@ -2986,62 +2152,58 @@
         <v>65535</v>
       </c>
       <c r="I5">
-        <v>38.2883</v>
+        <v>11.155099999999999</v>
       </c>
       <c r="J5">
-        <v>21.544599999999999</v>
+        <v>5.2057900000000004</v>
       </c>
       <c r="K5">
-        <v>3.20996E-3</v>
+        <v>7.9774500000000005E-3</v>
       </c>
       <c r="L5">
-        <v>0.32427499999999998</v>
+        <v>0.133329</v>
       </c>
       <c r="M5">
-        <v>14.4941</v>
+        <v>9.9107299999999992</v>
       </c>
       <c r="N5">
-        <v>39608</v>
+        <v>6206</v>
       </c>
       <c r="O5">
-        <v>233662</v>
+        <v>56413</v>
       </c>
       <c r="P5">
-        <v>16.951000000000001</v>
+        <v>11.000999999999999</v>
       </c>
       <c r="Q5">
         <v>15</v>
       </c>
       <c r="R5">
-        <v>1.1094999999999999</v>
+        <v>1.07866</v>
       </c>
       <c r="S5">
-        <v>-52.646799999999999</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T5">
-        <v>35.323399999999999</v>
+        <v>17.3354</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>40.09588058972718</v>
+        <v>11.433148794365955</v>
       </c>
       <c r="V5">
-        <v>38.2883</v>
-      </c>
-      <c r="W5">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>11.155099999999999</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6">
         <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>25</v>
       </c>
       <c r="D6">
         <v>1400</v>
@@ -3059,62 +2221,58 @@
         <v>65535</v>
       </c>
       <c r="I6">
-        <v>47.786099999999998</v>
+        <v>11.378500000000001</v>
       </c>
       <c r="J6">
-        <v>26.930499999999999</v>
+        <v>5.2057900000000004</v>
       </c>
       <c r="K6">
-        <v>1.23263E-2</v>
+        <v>7.9774500000000005E-3</v>
       </c>
       <c r="L6">
-        <v>0.52263400000000004</v>
+        <v>0.12881300000000001</v>
       </c>
       <c r="M6">
-        <v>23.0915</v>
+        <v>8.0487699999999993</v>
       </c>
       <c r="N6">
-        <v>87696</v>
+        <v>4938</v>
       </c>
       <c r="O6">
-        <v>292080</v>
+        <v>56413</v>
       </c>
       <c r="P6">
-        <v>30.024699999999999</v>
+        <v>8.7532999999999994</v>
       </c>
       <c r="Q6">
         <v>15</v>
       </c>
       <c r="R6">
-        <v>1.0733299999999999</v>
+        <v>1.1269899999999999</v>
       </c>
       <c r="S6">
-        <v>-52.646799999999999</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T6">
-        <v>35.355600000000003</v>
+        <v>14.430999999999999</v>
       </c>
       <c r="U6">
         <f t="shared" si="0"/>
-        <v>48.532110403643827</v>
+        <v>12.801684339618824</v>
       </c>
       <c r="V6">
-        <v>47.786099999999998</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>11.378500000000001</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>1400</v>
@@ -3132,62 +2290,62 @@
         <v>65535</v>
       </c>
       <c r="I7">
-        <v>57.730400000000003</v>
+        <v>18.0457</v>
       </c>
       <c r="J7">
-        <v>36.535600000000002</v>
+        <v>10.7767</v>
       </c>
       <c r="K7">
-        <v>0.46201300000000001</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2.9915500000000002</v>
+        <v>7.3201500000000003E-2</v>
       </c>
       <c r="M7">
-        <v>40.525100000000002</v>
+        <v>0.137549</v>
       </c>
       <c r="N7">
-        <v>270250</v>
+        <v>161</v>
       </c>
       <c r="O7">
-        <v>396620</v>
+        <v>116888</v>
       </c>
       <c r="P7">
-        <v>68.138300000000001</v>
+        <v>0.137739</v>
       </c>
       <c r="Q7">
         <v>15</v>
       </c>
       <c r="R7">
-        <v>1.0358000000000001</v>
+        <v>1.19211</v>
       </c>
       <c r="S7">
         <v>-52.646799999999999</v>
       </c>
       <c r="T7">
-        <v>35.722299999999997</v>
+        <v>35.318199999999997</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>61.261088521224956</v>
+        <v>17.359290834494285</v>
       </c>
       <c r="V7">
-        <v>57.730400000000003</v>
+        <v>18.0457</v>
       </c>
       <c r="W7">
-        <f t="shared" si="1"/>
+        <f>100*(1-EXP(-(6.207*$C7 - 0.0057*$S7 + 30.9139*$A7 - 0.3386)))</f>
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
       <c r="C8">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>1400</v>
@@ -3205,62 +2363,58 @@
         <v>65535</v>
       </c>
       <c r="I8">
-        <v>70.084500000000006</v>
+        <v>20.027000000000001</v>
       </c>
       <c r="J8">
-        <v>46.849899999999998</v>
+        <v>10.7767</v>
       </c>
       <c r="K8">
-        <v>1.25021</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>8.4782100000000007</v>
+        <v>9.8025200000000007E-2</v>
       </c>
       <c r="M8">
-        <v>47.791400000000003</v>
+        <v>5.1319299999999997</v>
       </c>
       <c r="N8">
-        <v>458921</v>
+        <v>6323</v>
       </c>
       <c r="O8">
-        <v>501337</v>
+        <v>116886</v>
       </c>
       <c r="P8">
-        <v>91.539400000000001</v>
+        <v>5.4095399999999998</v>
       </c>
       <c r="Q8">
         <v>15</v>
       </c>
       <c r="R8">
-        <v>1.12784</v>
+        <v>1.15202</v>
       </c>
       <c r="S8">
-        <v>-52.646799999999999</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T8">
-        <v>36.133499999999998</v>
+        <v>26.3062</v>
       </c>
       <c r="U8">
         <f t="shared" si="0"/>
-        <v>73.198278059855596</v>
+        <v>21.211241622123296</v>
       </c>
       <c r="V8">
-        <v>70.084500000000006</v>
-      </c>
-      <c r="W8">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>20.027000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>1400</v>
@@ -3278,62 +2432,58 @@
         <v>65535</v>
       </c>
       <c r="I9">
-        <v>77.872699999999995</v>
+        <v>19.834900000000001</v>
       </c>
       <c r="J9">
-        <v>54.803699999999999</v>
+        <v>10.5923</v>
       </c>
       <c r="K9">
-        <v>2.1550699999999998</v>
+        <v>1.3064000000000001E-3</v>
       </c>
       <c r="L9">
-        <v>10.5283</v>
+        <v>0.102773</v>
       </c>
       <c r="M9">
-        <v>46.2498</v>
+        <v>6.0826399999999996</v>
       </c>
       <c r="N9">
-        <v>491336</v>
+        <v>7437</v>
       </c>
       <c r="O9">
-        <v>571016</v>
+        <v>114829</v>
       </c>
       <c r="P9">
-        <v>86.045900000000003</v>
+        <v>6.4765899999999998</v>
       </c>
       <c r="Q9">
         <v>15</v>
       </c>
       <c r="R9">
-        <v>1.25271</v>
+        <v>1.14764</v>
       </c>
       <c r="S9">
-        <v>-52.646799999999999</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T9">
-        <v>36.632300000000001</v>
+        <v>21.0504</v>
       </c>
       <c r="U9">
         <f t="shared" si="0"/>
-        <v>82.694866040660486</v>
+        <v>23.367235435120978</v>
       </c>
       <c r="V9">
-        <v>77.872699999999995</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>19.834900000000001</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D10">
         <v>1400</v>
@@ -3351,62 +2501,58 @@
         <v>65535</v>
       </c>
       <c r="I10">
-        <v>83.590400000000002</v>
+        <v>22.5413</v>
       </c>
       <c r="J10">
-        <v>53.903100000000002</v>
+        <v>10.592599999999999</v>
       </c>
       <c r="K10">
-        <v>2.4186299999999998</v>
+        <v>2.6126399999999998E-3</v>
       </c>
       <c r="L10">
-        <v>12.433400000000001</v>
+        <v>0.13994400000000001</v>
       </c>
       <c r="M10">
-        <v>44.445500000000003</v>
+        <v>10.3019</v>
       </c>
       <c r="N10">
-        <v>443723</v>
+        <v>13189</v>
       </c>
       <c r="O10">
-        <v>554629</v>
+        <v>114836</v>
       </c>
       <c r="P10">
-        <v>80.003600000000006</v>
+        <v>11.485099999999999</v>
       </c>
       <c r="Q10">
         <v>15</v>
       </c>
       <c r="R10">
-        <v>1.3283400000000001</v>
+        <v>1.08134</v>
       </c>
       <c r="S10">
-        <v>-52.646799999999999</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T10">
-        <v>36.738900000000001</v>
+        <v>17.332599999999999</v>
       </c>
       <c r="U10">
         <f t="shared" si="0"/>
-        <v>86.351096085559902</v>
+        <v>24.855021683696215</v>
       </c>
       <c r="V10">
-        <v>83.590400000000002</v>
-      </c>
-      <c r="W10">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>22.5413</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
         <v>25</v>
       </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
       <c r="C11">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>1400</v>
@@ -3424,62 +2570,58 @@
         <v>65535</v>
       </c>
       <c r="I11">
-        <v>88.548299999999998</v>
+        <v>22.463000000000001</v>
       </c>
       <c r="J11">
-        <v>55.014499999999998</v>
+        <v>10.025600000000001</v>
       </c>
       <c r="K11">
-        <v>2.5572499999999998</v>
+        <v>5.8000599999999999E-2</v>
       </c>
       <c r="L11">
-        <v>15.946400000000001</v>
+        <v>0.19667899999999999</v>
       </c>
       <c r="M11">
-        <v>42.023099999999999</v>
+        <v>13.1676</v>
       </c>
       <c r="N11">
-        <v>401780</v>
+        <v>16474</v>
       </c>
       <c r="O11">
-        <v>554314</v>
+        <v>108636</v>
       </c>
       <c r="P11">
-        <v>72.482399999999998</v>
+        <v>15.164400000000001</v>
       </c>
       <c r="Q11">
         <v>15</v>
       </c>
       <c r="R11">
-        <v>1.4584900000000001</v>
+        <v>1.10825</v>
       </c>
       <c r="S11">
-        <v>-52.646799999999999</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T11">
-        <v>36.990600000000001</v>
+        <v>14.479799999999999</v>
       </c>
       <c r="U11">
         <f t="shared" si="0"/>
-        <v>87.758761466878511</v>
+        <v>25.985631585286583</v>
       </c>
       <c r="V11">
-        <v>88.548299999999998</v>
-      </c>
-      <c r="W11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>22.463000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>5</v>
       </c>
       <c r="C12">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>1400</v>
@@ -3497,62 +2639,62 @@
         <v>65535</v>
       </c>
       <c r="I12">
-        <v>89.776300000000006</v>
+        <v>27.614000000000001</v>
       </c>
       <c r="J12">
-        <v>48.9285</v>
+        <v>16.161999999999999</v>
       </c>
       <c r="K12">
-        <v>2.3839899999999998</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>17.814</v>
+        <v>0.13838800000000001</v>
       </c>
       <c r="M12">
-        <v>42.495800000000003</v>
+        <v>5.20845</v>
       </c>
       <c r="N12">
-        <v>359744</v>
+        <v>9631</v>
       </c>
       <c r="O12">
-        <v>486796</v>
+        <v>175280</v>
       </c>
       <c r="P12">
-        <v>73.900400000000005</v>
+        <v>5.4946400000000004</v>
       </c>
       <c r="Q12">
         <v>15</v>
       </c>
       <c r="R12">
-        <v>1.5004</v>
+        <v>1.1623699999999999</v>
       </c>
       <c r="S12">
         <v>-52.646799999999999</v>
       </c>
       <c r="T12">
-        <v>36.9422</v>
+        <v>35.317799999999998</v>
       </c>
       <c r="U12">
         <f t="shared" si="0"/>
-        <v>88.300719112165922</v>
+        <v>29.750879078150671</v>
       </c>
       <c r="V12">
-        <v>89.776300000000006</v>
+        <v>27.614000000000001</v>
       </c>
       <c r="W12">
-        <f t="shared" si="1"/>
+        <f>100*(1-EXP(-(6.207*$C12 - 0.0057*$S12 + 30.9139*$A12 - 0.3386)))</f>
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>1400</v>
@@ -3570,62 +2712,58 @@
         <v>65535</v>
       </c>
       <c r="I13">
-        <v>90.846500000000006</v>
+        <v>29.929099999999998</v>
       </c>
       <c r="J13">
-        <v>40.3003</v>
+        <v>16.156300000000002</v>
       </c>
       <c r="K13">
-        <v>3.0872899999999999</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>24.270600000000002</v>
+        <v>0.106208</v>
       </c>
       <c r="M13">
-        <v>43.570599999999999</v>
+        <v>5.3336699999999997</v>
       </c>
       <c r="N13">
-        <v>310843</v>
+        <v>9873</v>
       </c>
       <c r="O13">
-        <v>402580</v>
+        <v>175234</v>
       </c>
       <c r="P13">
-        <v>77.212699999999998</v>
+        <v>5.6341799999999997</v>
       </c>
       <c r="Q13">
         <v>15</v>
       </c>
       <c r="R13">
-        <v>1.50186</v>
+        <v>1.1539699999999999</v>
       </c>
       <c r="S13">
-        <v>-52.646799999999999</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T13">
-        <v>37.158700000000003</v>
+        <v>26.305</v>
       </c>
       <c r="U13">
         <f t="shared" si="0"/>
-        <v>88.509375297921068</v>
+        <v>32.933152067726155</v>
       </c>
       <c r="V13">
-        <v>90.846500000000006</v>
-      </c>
-      <c r="W13">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>29.929099999999998</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>1400</v>
@@ -3643,62 +2781,58 @@
         <v>65535</v>
       </c>
       <c r="I14">
-        <v>90.504400000000004</v>
+        <v>29.875800000000002</v>
       </c>
       <c r="J14">
-        <v>42.448599999999999</v>
+        <v>15.9735</v>
       </c>
       <c r="K14">
-        <v>3.0270700000000001</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>23.2728</v>
+        <v>0.12235699999999999</v>
       </c>
       <c r="M14">
-        <v>43.3795</v>
+        <v>6.6430600000000002</v>
       </c>
       <c r="N14">
-        <v>323369</v>
+        <v>12323</v>
       </c>
       <c r="O14">
-        <v>422073</v>
+        <v>173179</v>
       </c>
       <c r="P14">
-        <v>76.614500000000007</v>
+        <v>7.1157599999999999</v>
       </c>
       <c r="Q14">
         <v>15</v>
       </c>
       <c r="R14">
-        <v>1.5224200000000001</v>
+        <v>1.14777</v>
       </c>
       <c r="S14">
-        <v>-52.646799999999999</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T14">
-        <v>37.303800000000003</v>
+        <v>21.048100000000002</v>
       </c>
       <c r="U14">
         <f t="shared" si="0"/>
-        <v>88.58970888899124</v>
+        <v>34.714317314911874</v>
       </c>
       <c r="V14">
-        <v>90.504400000000004</v>
-      </c>
-      <c r="W14">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <v>29.875800000000002</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>1400</v>
@@ -3716,58 +2850,58 @@
         <v>65535</v>
       </c>
       <c r="I15">
-        <v>10.106299999999999</v>
+        <v>34.300400000000003</v>
       </c>
       <c r="J15">
-        <v>5.3879400000000004</v>
+        <v>15.9719</v>
       </c>
       <c r="K15">
-        <v>7.7002099999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>9.1091199999999997E-2</v>
+        <v>0.20555100000000001</v>
       </c>
       <c r="M15">
-        <v>4.7833899999999998</v>
+        <v>13.6473</v>
       </c>
       <c r="N15">
-        <v>2936</v>
+        <v>27366</v>
       </c>
       <c r="O15">
-        <v>58443</v>
+        <v>173157</v>
       </c>
       <c r="P15">
-        <v>5.0236999999999998</v>
+        <v>15.8042</v>
       </c>
       <c r="Q15">
         <v>15</v>
       </c>
       <c r="R15">
-        <v>1.14802</v>
+        <v>1.0632600000000001</v>
       </c>
       <c r="S15">
-        <v>-61.677700000000002</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T15">
-        <v>26.302199999999999</v>
+        <v>17.330200000000001</v>
       </c>
       <c r="U15">
-        <f t="shared" ref="U3:U66" si="2">90.504*(1-EXP(-(-0.0052*$C15 - 0.0062*$S15 + 0.2169*$A15 - 0.4879)))</f>
-        <v>7.4083537639594885</v>
+        <f t="shared" si="0"/>
+        <v>35.943445684959684</v>
       </c>
       <c r="V15">
-        <v>10.106299999999999</v>
+        <v>34.300400000000003</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>1400</v>
@@ -3785,58 +2919,58 @@
         <v>65535</v>
       </c>
       <c r="I16">
-        <v>20.027000000000001</v>
+        <v>34.715699999999998</v>
       </c>
       <c r="J16">
-        <v>10.7767</v>
+        <v>15.762600000000001</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>5.2699499999999998E-3</v>
       </c>
       <c r="L16">
-        <v>9.8025200000000007E-2</v>
+        <v>0.22498000000000001</v>
       </c>
       <c r="M16">
-        <v>5.1319299999999997</v>
+        <v>11.7529</v>
       </c>
       <c r="N16">
-        <v>6323</v>
+        <v>22747</v>
       </c>
       <c r="O16">
-        <v>116886</v>
+        <v>170797</v>
       </c>
       <c r="P16">
-        <v>5.4095399999999998</v>
+        <v>13.318099999999999</v>
       </c>
       <c r="Q16">
         <v>15</v>
       </c>
       <c r="R16">
-        <v>1.15202</v>
+        <v>1.10782</v>
       </c>
       <c r="S16">
-        <v>-61.677700000000002</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T16">
-        <v>26.3062</v>
+        <v>14.4993</v>
       </c>
       <c r="U16">
-        <f t="shared" si="2"/>
-        <v>21.849113565543391</v>
+        <f t="shared" si="0"/>
+        <v>36.877494313808391</v>
       </c>
       <c r="V16">
-        <v>20.027000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>34.715699999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D17">
         <v>1400</v>
@@ -3854,50 +2988,54 @@
         <v>65535</v>
       </c>
       <c r="I17">
-        <v>29.929099999999998</v>
+        <v>38.2883</v>
       </c>
       <c r="J17">
-        <v>16.156300000000002</v>
+        <v>21.544599999999999</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>3.20996E-3</v>
       </c>
       <c r="L17">
-        <v>0.106208</v>
+        <v>0.32427499999999998</v>
       </c>
       <c r="M17">
-        <v>5.3336699999999997</v>
+        <v>14.4941</v>
       </c>
       <c r="N17">
-        <v>9873</v>
+        <v>39608</v>
       </c>
       <c r="O17">
-        <v>175234</v>
+        <v>233662</v>
       </c>
       <c r="P17">
-        <v>5.6341799999999997</v>
+        <v>16.951000000000001</v>
       </c>
       <c r="Q17">
         <v>15</v>
       </c>
       <c r="R17">
-        <v>1.1539699999999999</v>
+        <v>1.1094999999999999</v>
       </c>
       <c r="S17">
-        <v>-61.677700000000002</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T17">
-        <v>26.305</v>
+        <v>35.323399999999999</v>
       </c>
       <c r="U17">
-        <f t="shared" si="2"/>
-        <v>33.780288893174493</v>
+        <f t="shared" si="0"/>
+        <v>39.988137740014665</v>
       </c>
       <c r="V17">
-        <v>29.929099999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+        <v>38.2883</v>
+      </c>
+      <c r="W17">
+        <f>100*(1-EXP(-(6.207*$C17 - 0.0057*$S17 + 30.9139*$A17 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>4</v>
       </c>
@@ -3959,22 +3097,22 @@
         <v>26.320499999999999</v>
       </c>
       <c r="U18">
-        <f t="shared" si="2"/>
-        <v>43.638007368836654</v>
+        <f t="shared" si="0"/>
+        <v>42.617159225103542</v>
       </c>
       <c r="V18">
         <v>40.900199999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D19">
         <v>1400</v>
@@ -3992,58 +3130,58 @@
         <v>65535</v>
       </c>
       <c r="I19">
-        <v>51.194499999999998</v>
+        <v>42.8964</v>
       </c>
       <c r="J19">
-        <v>26.9269</v>
+        <v>21.357900000000001</v>
       </c>
       <c r="K19">
-        <v>4.1594300000000001E-2</v>
+        <v>1.9431400000000001E-2</v>
       </c>
       <c r="L19">
-        <v>0.70301800000000003</v>
+        <v>0.35078300000000001</v>
       </c>
       <c r="M19">
-        <v>29.085999999999999</v>
+        <v>20.573899999999998</v>
       </c>
       <c r="N19">
-        <v>119818</v>
+        <v>59994</v>
       </c>
       <c r="O19">
-        <v>292126</v>
+        <v>231608</v>
       </c>
       <c r="P19">
-        <v>41.015900000000002</v>
+        <v>25.903300000000002</v>
       </c>
       <c r="Q19">
         <v>15</v>
       </c>
       <c r="R19">
-        <v>1.03661</v>
+        <v>1.0691900000000001</v>
       </c>
       <c r="S19">
-        <v>-61.677700000000002</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T19">
-        <v>26.374199999999998</v>
+        <v>21.1</v>
       </c>
       <c r="U19">
-        <f t="shared" si="2"/>
-        <v>51.782604265369315</v>
+        <f t="shared" si="0"/>
+        <v>44.08866142453288</v>
       </c>
       <c r="V19">
-        <v>51.194499999999998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
+        <v>42.8964</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C20">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D20">
         <v>1400</v>
@@ -4061,58 +3199,58 @@
         <v>65535</v>
       </c>
       <c r="I20">
-        <v>62.548999999999999</v>
+        <v>46.510100000000001</v>
       </c>
       <c r="J20">
-        <v>36.851799999999997</v>
+        <v>21.356999999999999</v>
       </c>
       <c r="K20">
-        <v>0.50115699999999996</v>
+        <v>7.7741399999999997E-3</v>
       </c>
       <c r="L20">
-        <v>4.0913599999999999</v>
+        <v>0.40173700000000001</v>
       </c>
       <c r="M20">
-        <v>44.249600000000001</v>
+        <v>21.924299999999999</v>
       </c>
       <c r="N20">
-        <v>317464</v>
+        <v>65023</v>
       </c>
       <c r="O20">
-        <v>399976</v>
+        <v>231556</v>
       </c>
       <c r="P20">
-        <v>79.370800000000003</v>
+        <v>28.0809</v>
       </c>
       <c r="Q20">
         <v>15</v>
       </c>
       <c r="R20">
-        <v>1.0528299999999999</v>
+        <v>1.02586</v>
       </c>
       <c r="S20">
-        <v>-61.677700000000002</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T20">
-        <v>26.841999999999999</v>
+        <v>17.366599999999998</v>
       </c>
       <c r="U20">
-        <f t="shared" si="2"/>
-        <v>64.071552997119383</v>
+        <f t="shared" si="0"/>
+        <v>45.104100672948526</v>
       </c>
       <c r="V20">
-        <v>62.548999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+        <v>46.510100000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B21">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>1400</v>
@@ -4130,58 +3268,58 @@
         <v>65535</v>
       </c>
       <c r="I21">
-        <v>72.8172</v>
+        <v>55.491399999999999</v>
       </c>
       <c r="J21">
-        <v>45.147399999999998</v>
+        <v>19.5532</v>
       </c>
       <c r="K21">
-        <v>1.46173</v>
+        <v>0.73683399999999999</v>
       </c>
       <c r="L21">
-        <v>10.7971</v>
+        <v>4.18133</v>
       </c>
       <c r="M21">
-        <v>45.616500000000002</v>
+        <v>50.155999999999999</v>
       </c>
       <c r="N21">
-        <v>403034</v>
+        <v>212890</v>
       </c>
       <c r="O21">
-        <v>480492</v>
+        <v>211566</v>
       </c>
       <c r="P21">
-        <v>83.879400000000004</v>
+        <v>100.626</v>
       </c>
       <c r="Q21">
         <v>15</v>
       </c>
       <c r="R21">
-        <v>1.1692899999999999</v>
+        <v>0.999807</v>
       </c>
       <c r="S21">
-        <v>-61.677700000000002</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T21">
-        <v>27.1402</v>
+        <v>14.500400000000001</v>
       </c>
       <c r="U21">
-        <f t="shared" si="2"/>
-        <v>75.596084572737468</v>
+        <f t="shared" si="0"/>
+        <v>45.875761030625341</v>
       </c>
       <c r="V21">
-        <v>72.8172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+        <v>55.491399999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C22">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>1400</v>
@@ -4199,58 +3337,62 @@
         <v>65535</v>
       </c>
       <c r="I22">
-        <v>81.631100000000004</v>
+        <v>47.786099999999998</v>
       </c>
       <c r="J22">
-        <v>50.441899999999997</v>
+        <v>26.930499999999999</v>
       </c>
       <c r="K22">
-        <v>2.11727</v>
+        <v>1.23263E-2</v>
       </c>
       <c r="L22">
-        <v>18.714200000000002</v>
+        <v>0.52263400000000004</v>
       </c>
       <c r="M22">
-        <v>43.949800000000003</v>
+        <v>23.0915</v>
       </c>
       <c r="N22">
-        <v>409506</v>
+        <v>87696</v>
       </c>
       <c r="O22">
-        <v>522252</v>
+        <v>292080</v>
       </c>
       <c r="P22">
-        <v>78.411600000000007</v>
+        <v>30.024699999999999</v>
       </c>
       <c r="Q22">
         <v>15</v>
       </c>
       <c r="R22">
-        <v>1.3031900000000001</v>
+        <v>1.0733299999999999</v>
       </c>
       <c r="S22">
-        <v>-61.677700000000002</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T22">
-        <v>27.639199999999999</v>
+        <v>35.355600000000003</v>
       </c>
       <c r="U22">
-        <f t="shared" si="2"/>
-        <v>84.7643840029546</v>
+        <f t="shared" si="0"/>
+        <v>48.445606052324024</v>
       </c>
       <c r="V22">
-        <v>81.631100000000004</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+        <v>47.786099999999998</v>
+      </c>
+      <c r="W22">
+        <f>100*(1-EXP(-(6.207*$C22 - 0.0057*$S22 + 30.9139*$A22 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="B23">
         <v>10</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D23">
         <v>1400</v>
@@ -4268,58 +3410,58 @@
         <v>65535</v>
       </c>
       <c r="I23">
-        <v>85.874099999999999</v>
+        <v>51.194499999999998</v>
       </c>
       <c r="J23">
-        <v>53.707299999999996</v>
+        <v>26.9269</v>
       </c>
       <c r="K23">
-        <v>2.4706999999999999</v>
+        <v>4.1594300000000001E-2</v>
       </c>
       <c r="L23">
-        <v>19.8218</v>
+        <v>0.70301800000000003</v>
       </c>
       <c r="M23">
-        <v>41.311399999999999</v>
+        <v>29.085999999999999</v>
       </c>
       <c r="N23">
-        <v>386904</v>
+        <v>119818</v>
       </c>
       <c r="O23">
-        <v>549652</v>
+        <v>292126</v>
       </c>
       <c r="P23">
-        <v>70.390699999999995</v>
+        <v>41.015900000000002</v>
       </c>
       <c r="Q23">
         <v>15</v>
       </c>
       <c r="R23">
-        <v>1.3800399999999999</v>
+        <v>1.03661</v>
       </c>
       <c r="S23">
         <v>-61.677700000000002</v>
       </c>
       <c r="T23">
-        <v>28.081099999999999</v>
+        <v>26.374199999999998</v>
       </c>
       <c r="U23">
-        <f t="shared" si="2"/>
-        <v>88.29422144616575</v>
+        <f t="shared" si="0"/>
+        <v>50.617561127108793</v>
       </c>
       <c r="V23">
-        <v>85.874099999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+        <v>51.194499999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
+      <c r="C24">
         <v>25</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-      <c r="C24">
-        <v>125</v>
       </c>
       <c r="D24">
         <v>1400</v>
@@ -4337,58 +3479,58 @@
         <v>65535</v>
       </c>
       <c r="I24">
-        <v>90.224500000000006</v>
+        <v>52.767699999999998</v>
       </c>
       <c r="J24">
-        <v>43.371200000000002</v>
+        <v>26.930800000000001</v>
       </c>
       <c r="K24">
-        <v>2.4353799999999999</v>
+        <v>6.0067500000000003E-2</v>
       </c>
       <c r="L24">
-        <v>31.7163</v>
+        <v>0.84127099999999999</v>
       </c>
       <c r="M24">
-        <v>39.817500000000003</v>
+        <v>31.883199999999999</v>
       </c>
       <c r="N24">
-        <v>288773</v>
+        <v>136786</v>
       </c>
       <c r="O24">
-        <v>436468</v>
+        <v>292236</v>
       </c>
       <c r="P24">
-        <v>66.161299999999997</v>
+        <v>46.806699999999999</v>
       </c>
       <c r="Q24">
         <v>15</v>
       </c>
       <c r="R24">
-        <v>1.4881200000000001</v>
+        <v>1.0209600000000001</v>
       </c>
       <c r="S24">
-        <v>-61.677700000000002</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T24">
-        <v>28.207899999999999</v>
+        <v>21.193200000000001</v>
       </c>
       <c r="U24">
-        <f t="shared" si="2"/>
-        <v>89.653225094588308</v>
+        <f t="shared" si="0"/>
+        <v>51.833236498243849</v>
       </c>
       <c r="V24">
-        <v>90.224500000000006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+        <v>52.767699999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
       <c r="A25">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C25">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="D25">
         <v>1400</v>
@@ -4406,58 +3548,58 @@
         <v>65535</v>
       </c>
       <c r="I25">
-        <v>89.726399999999998</v>
+        <v>55.146999999999998</v>
       </c>
       <c r="J25">
-        <v>47.193899999999999</v>
+        <v>26.134899999999998</v>
       </c>
       <c r="K25">
-        <v>2.5136400000000001</v>
+        <v>0.13542299999999999</v>
       </c>
       <c r="L25">
-        <v>27.448</v>
+        <v>1.18428</v>
       </c>
       <c r="M25">
-        <v>40.777000000000001</v>
+        <v>35.926900000000003</v>
       </c>
       <c r="N25">
-        <v>326189</v>
+        <v>159075</v>
       </c>
       <c r="O25">
-        <v>473744</v>
+        <v>283699</v>
       </c>
       <c r="P25">
-        <v>68.853399999999993</v>
+        <v>56.071800000000003</v>
       </c>
       <c r="Q25">
         <v>15</v>
       </c>
       <c r="R25">
-        <v>1.4955499999999999</v>
+        <v>0.97982000000000002</v>
       </c>
       <c r="S25">
-        <v>-61.677700000000002</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T25">
-        <v>28.1159</v>
+        <v>17.549299999999999</v>
       </c>
       <c r="U25">
-        <f t="shared" si="2"/>
-        <v>90.176447748928339</v>
+        <f t="shared" si="0"/>
+        <v>52.672137374954424</v>
       </c>
       <c r="V25">
-        <v>89.726399999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>55.146999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C26">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="D26">
         <v>1400</v>
@@ -4475,58 +3617,58 @@
         <v>65535</v>
       </c>
       <c r="I26">
-        <v>89.557299999999998</v>
+        <v>61.714399999999998</v>
       </c>
       <c r="J26">
-        <v>50.222900000000003</v>
+        <v>26.723099999999999</v>
       </c>
       <c r="K26">
-        <v>2.3092299999999999</v>
+        <v>0.29297299999999998</v>
       </c>
       <c r="L26">
-        <v>30.3901</v>
+        <v>1.96048</v>
       </c>
       <c r="M26">
-        <v>41.006999999999998</v>
+        <v>38.727600000000002</v>
       </c>
       <c r="N26">
-        <v>348784</v>
+        <v>183363</v>
       </c>
       <c r="O26">
-        <v>501763</v>
+        <v>290106</v>
       </c>
       <c r="P26">
-        <v>69.511700000000005</v>
+        <v>63.205500000000001</v>
       </c>
       <c r="Q26">
         <v>15</v>
       </c>
       <c r="R26">
-        <v>1.51183</v>
+        <v>1.0059199999999999</v>
       </c>
       <c r="S26">
-        <v>-61.677700000000002</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T26">
-        <v>27.9954</v>
+        <v>14.805899999999999</v>
       </c>
       <c r="U26">
-        <f t="shared" si="2"/>
-        <v>90.377890877011481</v>
+        <f t="shared" si="0"/>
+        <v>53.309641343397544</v>
       </c>
       <c r="V26">
-        <v>89.557299999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+        <v>61.714399999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="D27">
         <v>1400</v>
@@ -4544,58 +3686,62 @@
         <v>65535</v>
       </c>
       <c r="I27">
-        <v>89.909599999999998</v>
+        <v>57.730400000000003</v>
       </c>
       <c r="J27">
-        <v>48.381300000000003</v>
+        <v>36.535600000000002</v>
       </c>
       <c r="K27">
-        <v>3.0191400000000002</v>
+        <v>0.46201300000000001</v>
       </c>
       <c r="L27">
-        <v>28.368600000000001</v>
+        <v>2.9915500000000002</v>
       </c>
       <c r="M27">
-        <v>41.976300000000002</v>
+        <v>40.525100000000002</v>
       </c>
       <c r="N27">
-        <v>350465</v>
+        <v>270250</v>
       </c>
       <c r="O27">
-        <v>484446</v>
+        <v>396620</v>
       </c>
       <c r="P27">
-        <v>72.343500000000006</v>
+        <v>68.138300000000001</v>
       </c>
       <c r="Q27">
         <v>15</v>
       </c>
       <c r="R27">
-        <v>1.5185900000000001</v>
+        <v>1.0358000000000001</v>
       </c>
       <c r="S27">
-        <v>-61.677700000000002</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T27">
-        <v>28.028300000000002</v>
+        <v>35.722299999999997</v>
       </c>
       <c r="U27">
-        <f t="shared" si="2"/>
-        <v>90.455447407707013</v>
+        <f t="shared" si="0"/>
+        <v>61.205073029633212</v>
       </c>
       <c r="V27">
-        <v>89.909599999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+        <v>57.730400000000003</v>
+      </c>
+      <c r="W27">
+        <f>100*(1-EXP(-(6.207*$C27 - 0.0057*$S27 + 30.9139*$A27 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23">
       <c r="A28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>1400</v>
@@ -4613,58 +3759,58 @@
         <v>65535</v>
       </c>
       <c r="I28">
-        <v>9.85351</v>
+        <v>62.548999999999999</v>
       </c>
       <c r="J28">
-        <v>5.2057900000000004</v>
+        <v>36.851799999999997</v>
       </c>
       <c r="K28">
-        <v>7.9774500000000005E-3</v>
+        <v>0.50115699999999996</v>
       </c>
       <c r="L28">
-        <v>0.100671</v>
+        <v>4.0913599999999999</v>
       </c>
       <c r="M28">
-        <v>6.3311500000000001</v>
+        <v>44.249600000000001</v>
       </c>
       <c r="N28">
-        <v>3813</v>
+        <v>317464</v>
       </c>
       <c r="O28">
-        <v>56413</v>
+        <v>399976</v>
       </c>
       <c r="P28">
-        <v>6.75908</v>
+        <v>79.370800000000003</v>
       </c>
       <c r="Q28">
         <v>15</v>
       </c>
       <c r="R28">
-        <v>1.1375900000000001</v>
+        <v>1.0528299999999999</v>
       </c>
       <c r="S28">
-        <v>-66.960400000000007</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T28">
-        <v>21.043800000000001</v>
+        <v>26.841999999999999</v>
       </c>
       <c r="U28">
-        <f t="shared" si="2"/>
-        <v>10.085876405500846</v>
+        <f t="shared" si="0"/>
+        <v>62.687469059872143</v>
       </c>
       <c r="V28">
-        <v>9.85351</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+        <v>62.548999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23">
       <c r="A29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B29">
         <v>15</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D29">
         <v>1400</v>
@@ -4682,58 +3828,58 @@
         <v>65535</v>
       </c>
       <c r="I29">
-        <v>19.834900000000001</v>
+        <v>62.839599999999997</v>
       </c>
       <c r="J29">
-        <v>10.5923</v>
+        <v>35.434899999999999</v>
       </c>
       <c r="K29">
-        <v>1.3064000000000001E-3</v>
+        <v>0.56203599999999998</v>
       </c>
       <c r="L29">
-        <v>0.102773</v>
+        <v>3.8171900000000001</v>
       </c>
       <c r="M29">
-        <v>6.0826399999999996</v>
+        <v>43.212499999999999</v>
       </c>
       <c r="N29">
-        <v>7437</v>
+        <v>291444</v>
       </c>
       <c r="O29">
-        <v>114829</v>
+        <v>382999</v>
       </c>
       <c r="P29">
-        <v>6.4765899999999998</v>
+        <v>76.095200000000006</v>
       </c>
       <c r="Q29">
         <v>15</v>
       </c>
       <c r="R29">
-        <v>1.14764</v>
+        <v>1.06531</v>
       </c>
       <c r="S29">
         <v>-66.960400000000007</v>
       </c>
       <c r="T29">
-        <v>21.0504</v>
+        <v>21.593900000000001</v>
       </c>
       <c r="U29">
-        <f t="shared" si="2"/>
-        <v>24.061323485164653</v>
+        <f t="shared" si="0"/>
+        <v>63.517188037557922</v>
       </c>
       <c r="V29">
-        <v>19.834900000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+        <v>62.839599999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23">
       <c r="A30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>1400</v>
@@ -4751,58 +3897,58 @@
         <v>65535</v>
       </c>
       <c r="I30">
-        <v>29.875800000000002</v>
+        <v>66.2089</v>
       </c>
       <c r="J30">
-        <v>15.9735</v>
+        <v>33.621200000000002</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>0.77761999999999998</v>
       </c>
       <c r="L30">
-        <v>0.12235699999999999</v>
+        <v>4.6535700000000002</v>
       </c>
       <c r="M30">
-        <v>6.6430600000000002</v>
+        <v>43.9754</v>
       </c>
       <c r="N30">
-        <v>12323</v>
+        <v>283859</v>
       </c>
       <c r="O30">
-        <v>173179</v>
+        <v>361636</v>
       </c>
       <c r="P30">
-        <v>7.1157599999999999</v>
+        <v>78.492999999999995</v>
       </c>
       <c r="Q30">
         <v>15</v>
       </c>
       <c r="R30">
-        <v>1.14777</v>
+        <v>1.05192</v>
       </c>
       <c r="S30">
-        <v>-66.960400000000007</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T30">
-        <v>21.048100000000002</v>
+        <v>18.141100000000002</v>
       </c>
       <c r="U30">
-        <f t="shared" si="2"/>
-        <v>35.608050366613789</v>
+        <f t="shared" si="0"/>
+        <v>64.089752057798052</v>
       </c>
       <c r="V30">
-        <v>29.875800000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+        <v>66.2089</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23">
       <c r="A31">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D31">
         <v>1400</v>
@@ -4820,58 +3966,58 @@
         <v>65535</v>
       </c>
       <c r="I31">
-        <v>42.8964</v>
+        <v>67.334000000000003</v>
       </c>
       <c r="J31">
-        <v>21.357900000000001</v>
+        <v>27.108000000000001</v>
       </c>
       <c r="K31">
-        <v>1.9431400000000001E-2</v>
+        <v>1.58396</v>
       </c>
       <c r="L31">
-        <v>0.35078300000000001</v>
+        <v>14.362399999999999</v>
       </c>
       <c r="M31">
-        <v>20.573899999999998</v>
+        <v>46.2849</v>
       </c>
       <c r="N31">
-        <v>59994</v>
+        <v>246957</v>
       </c>
       <c r="O31">
-        <v>231608</v>
+        <v>286602</v>
       </c>
       <c r="P31">
-        <v>25.903300000000002</v>
+        <v>86.167199999999994</v>
       </c>
       <c r="Q31">
         <v>15</v>
       </c>
       <c r="R31">
-        <v>1.0691900000000001</v>
+        <v>1.19346</v>
       </c>
       <c r="S31">
-        <v>-66.960400000000007</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T31">
-        <v>21.1</v>
+        <v>14.797000000000001</v>
       </c>
       <c r="U31">
-        <f t="shared" si="2"/>
-        <v>45.14813169029388</v>
+        <f t="shared" si="0"/>
+        <v>64.524859285867819</v>
       </c>
       <c r="V31">
-        <v>42.8964</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>67.334000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23">
       <c r="A32">
+        <v>10</v>
+      </c>
+      <c r="B32">
         <v>5</v>
       </c>
-      <c r="B32">
-        <v>15</v>
-      </c>
       <c r="C32">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D32">
         <v>1400</v>
@@ -4889,58 +4035,62 @@
         <v>65535</v>
       </c>
       <c r="I32">
-        <v>52.767699999999998</v>
+        <v>70.084500000000006</v>
       </c>
       <c r="J32">
-        <v>26.930800000000001</v>
+        <v>46.849899999999998</v>
       </c>
       <c r="K32">
-        <v>6.0067500000000003E-2</v>
+        <v>1.25021</v>
       </c>
       <c r="L32">
-        <v>0.84127099999999999</v>
+        <v>8.4782100000000007</v>
       </c>
       <c r="M32">
-        <v>31.883199999999999</v>
+        <v>47.791400000000003</v>
       </c>
       <c r="N32">
-        <v>136786</v>
+        <v>458921</v>
       </c>
       <c r="O32">
-        <v>292236</v>
+        <v>501337</v>
       </c>
       <c r="P32">
-        <v>46.806699999999999</v>
+        <v>91.539400000000001</v>
       </c>
       <c r="Q32">
         <v>15</v>
       </c>
       <c r="R32">
-        <v>1.0209600000000001</v>
+        <v>1.12784</v>
       </c>
       <c r="S32">
-        <v>-66.960400000000007</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T32">
-        <v>21.193200000000001</v>
+        <v>36.133499999999998</v>
       </c>
       <c r="U32">
-        <f t="shared" si="2"/>
-        <v>53.030291942014273</v>
+        <f t="shared" si="0"/>
+        <v>73.168421684466864</v>
       </c>
       <c r="V32">
-        <v>52.767699999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>70.084500000000006</v>
+      </c>
+      <c r="W32">
+        <f>100*(1-EXP(-(6.207*$C32 - 0.0057*$S32 + 30.9139*$A32 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23">
       <c r="A33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B33">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D33">
         <v>1400</v>
@@ -4958,50 +4108,50 @@
         <v>65535</v>
       </c>
       <c r="I33">
-        <v>62.839599999999997</v>
+        <v>72.8172</v>
       </c>
       <c r="J33">
-        <v>35.434899999999999</v>
+        <v>45.147399999999998</v>
       </c>
       <c r="K33">
-        <v>0.56203599999999998</v>
+        <v>1.46173</v>
       </c>
       <c r="L33">
-        <v>3.8171900000000001</v>
+        <v>10.7971</v>
       </c>
       <c r="M33">
-        <v>43.212499999999999</v>
+        <v>45.616500000000002</v>
       </c>
       <c r="N33">
-        <v>291444</v>
+        <v>403034</v>
       </c>
       <c r="O33">
-        <v>382999</v>
+        <v>480492</v>
       </c>
       <c r="P33">
-        <v>76.095200000000006</v>
+        <v>83.879400000000004</v>
       </c>
       <c r="Q33">
         <v>15</v>
       </c>
       <c r="R33">
-        <v>1.06531</v>
+        <v>1.1692899999999999</v>
       </c>
       <c r="S33">
-        <v>-66.960400000000007</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T33">
-        <v>21.593900000000001</v>
+        <v>27.1402</v>
       </c>
       <c r="U33">
-        <f t="shared" si="2"/>
-        <v>64.923263989540303</v>
+        <f t="shared" si="0"/>
+        <v>74.004283240917346</v>
       </c>
       <c r="V33">
-        <v>62.839599999999997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22">
+        <v>72.8172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23">
       <c r="A34">
         <v>10</v>
       </c>
@@ -5063,22 +4213,22 @@
         <v>21.9316</v>
       </c>
       <c r="U34">
-        <f t="shared" si="2"/>
-        <v>76.076450066030503</v>
+        <f t="shared" si="0"/>
+        <v>74.472127313592807</v>
       </c>
       <c r="V34">
         <v>72.9298</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:23">
       <c r="A35">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C35">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D35">
         <v>1400</v>
@@ -5096,58 +4246,58 @@
         <v>65535</v>
       </c>
       <c r="I35">
-        <v>80.255600000000001</v>
+        <v>77.522599999999997</v>
       </c>
       <c r="J35">
-        <v>51.718600000000002</v>
+        <v>41.662500000000001</v>
       </c>
       <c r="K35">
-        <v>1.64733</v>
+        <v>1.52654</v>
       </c>
       <c r="L35">
-        <v>13.424200000000001</v>
+        <v>12.141400000000001</v>
       </c>
       <c r="M35">
-        <v>41.796300000000002</v>
+        <v>44.040900000000001</v>
       </c>
       <c r="N35">
-        <v>381077</v>
+        <v>343927</v>
       </c>
       <c r="O35">
-        <v>530672</v>
+        <v>436999</v>
       </c>
       <c r="P35">
-        <v>71.810299999999998</v>
+        <v>78.701999999999998</v>
       </c>
       <c r="Q35">
         <v>15</v>
       </c>
       <c r="R35">
-        <v>1.3403099999999999</v>
+        <v>1.21699</v>
       </c>
       <c r="S35">
-        <v>-66.960400000000007</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T35">
-        <v>22.360299999999999</v>
+        <v>18.357700000000001</v>
       </c>
       <c r="U35">
-        <f t="shared" si="2"/>
-        <v>84.949326926945915</v>
+        <f t="shared" si="0"/>
+        <v>74.794972385599863</v>
       </c>
       <c r="V35">
-        <v>80.255600000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22">
+        <v>77.522599999999997</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23">
       <c r="A36">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B36">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C36">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D36">
         <v>1400</v>
@@ -5165,58 +4315,58 @@
         <v>65535</v>
       </c>
       <c r="I36">
-        <v>86.286199999999994</v>
+        <v>79.526300000000006</v>
       </c>
       <c r="J36">
-        <v>49.794199999999996</v>
+        <v>33.062600000000003</v>
       </c>
       <c r="K36">
-        <v>1.24915</v>
+        <v>1.8160000000000001</v>
       </c>
       <c r="L36">
-        <v>20.2654</v>
+        <v>21.401700000000002</v>
       </c>
       <c r="M36">
-        <v>37.760599999999997</v>
+        <v>47.088999999999999</v>
       </c>
       <c r="N36">
-        <v>300588</v>
+        <v>308208</v>
       </c>
       <c r="O36">
-        <v>495448</v>
+        <v>346314</v>
       </c>
       <c r="P36">
-        <v>60.669899999999998</v>
+        <v>88.996700000000004</v>
       </c>
       <c r="Q36">
         <v>15</v>
       </c>
       <c r="R36">
-        <v>1.5270300000000001</v>
+        <v>1.20096</v>
       </c>
       <c r="S36">
-        <v>-66.960400000000007</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T36">
-        <v>22.439</v>
+        <v>15.4857</v>
       </c>
       <c r="U36">
-        <f t="shared" si="2"/>
-        <v>88.365425322405869</v>
+        <f t="shared" si="0"/>
+        <v>75.040311281184088</v>
       </c>
       <c r="V36">
-        <v>86.286199999999994</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22">
+        <v>79.526300000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
       <c r="A37">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="D37">
         <v>1400</v>
@@ -5234,58 +4384,62 @@
         <v>65535</v>
       </c>
       <c r="I37">
-        <v>85.724000000000004</v>
+        <v>77.872699999999995</v>
       </c>
       <c r="J37">
-        <v>45.468299999999999</v>
+        <v>54.803699999999999</v>
       </c>
       <c r="K37">
-        <v>1.63368</v>
+        <v>2.1550699999999998</v>
       </c>
       <c r="L37">
-        <v>22.235900000000001</v>
+        <v>10.5283</v>
       </c>
       <c r="M37">
-        <v>40.140999999999998</v>
+        <v>46.2498</v>
       </c>
       <c r="N37">
-        <v>302312</v>
+        <v>491336</v>
       </c>
       <c r="O37">
-        <v>450813</v>
+        <v>571016</v>
       </c>
       <c r="P37">
-        <v>67.059299999999993</v>
+        <v>86.045900000000003</v>
       </c>
       <c r="Q37">
         <v>15</v>
       </c>
       <c r="R37">
-        <v>1.52363</v>
+        <v>1.25271</v>
       </c>
       <c r="S37">
-        <v>-66.960400000000007</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T37">
-        <v>22.544599999999999</v>
+        <v>36.632300000000001</v>
       </c>
       <c r="U37">
-        <f t="shared" si="2"/>
-        <v>89.680638914388496</v>
+        <f t="shared" si="0"/>
+        <v>82.682822508880335</v>
       </c>
       <c r="V37">
-        <v>85.724000000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22">
+        <v>77.872699999999995</v>
+      </c>
+      <c r="W37">
+        <f>100*(1-EXP(-(6.207*$C37 - 0.0057*$S37 + 30.9139*$A37 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
       <c r="A38">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="D38">
         <v>1400</v>
@@ -5303,58 +4457,58 @@
         <v>65535</v>
       </c>
       <c r="I38">
-        <v>85.069900000000004</v>
+        <v>81.631100000000004</v>
       </c>
       <c r="J38">
-        <v>44.584499999999998</v>
+        <v>50.441899999999997</v>
       </c>
       <c r="K38">
-        <v>1.96347</v>
+        <v>2.11727</v>
       </c>
       <c r="L38">
-        <v>21.029599999999999</v>
+        <v>18.714200000000002</v>
       </c>
       <c r="M38">
-        <v>41.106299999999997</v>
+        <v>43.949800000000003</v>
       </c>
       <c r="N38">
-        <v>307194</v>
+        <v>409506</v>
       </c>
       <c r="O38">
-        <v>440123</v>
+        <v>522252</v>
       </c>
       <c r="P38">
-        <v>69.797300000000007</v>
+        <v>78.411600000000007</v>
       </c>
       <c r="Q38">
         <v>15</v>
       </c>
       <c r="R38">
-        <v>1.5342100000000001</v>
+        <v>1.3031900000000001</v>
       </c>
       <c r="S38">
-        <v>-66.960400000000007</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T38">
-        <v>22.780899999999999</v>
+        <v>27.639199999999999</v>
       </c>
       <c r="U38">
-        <f t="shared" si="2"/>
-        <v>90.187002195620295</v>
+        <f t="shared" si="0"/>
+        <v>83.004497919970987</v>
       </c>
       <c r="V38">
-        <v>85.069900000000004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22">
+        <v>81.631100000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
       <c r="A39">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B39">
         <v>15</v>
       </c>
       <c r="C39">
-        <v>175</v>
+        <v>75</v>
       </c>
       <c r="D39">
         <v>1400</v>
@@ -5372,58 +4526,58 @@
         <v>65535</v>
       </c>
       <c r="I39">
-        <v>86.011600000000001</v>
+        <v>80.255600000000001</v>
       </c>
       <c r="J39">
-        <v>37.925800000000002</v>
+        <v>51.718600000000002</v>
       </c>
       <c r="K39">
-        <v>2.3621400000000001</v>
+        <v>1.64733</v>
       </c>
       <c r="L39">
-        <v>28.040199999999999</v>
+        <v>13.424200000000001</v>
       </c>
       <c r="M39">
-        <v>42.6</v>
+        <v>41.796300000000002</v>
       </c>
       <c r="N39">
-        <v>277500</v>
+        <v>381077</v>
       </c>
       <c r="O39">
-        <v>373909</v>
+        <v>530672</v>
       </c>
       <c r="P39">
-        <v>74.215900000000005</v>
+        <v>71.810299999999998</v>
       </c>
       <c r="Q39">
         <v>15</v>
       </c>
       <c r="R39">
-        <v>1.5398799999999999</v>
+        <v>1.3403099999999999</v>
       </c>
       <c r="S39">
         <v>-66.960400000000007</v>
       </c>
       <c r="T39">
-        <v>23.2805</v>
+        <v>22.360299999999999</v>
       </c>
       <c r="U39">
-        <f t="shared" si="2"/>
-        <v>90.381954387524985</v>
+        <f t="shared" si="0"/>
+        <v>83.184544404036231</v>
       </c>
       <c r="V39">
-        <v>86.011600000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22">
+        <v>80.255600000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
       <c r="A40">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C40">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="D40">
         <v>1400</v>
@@ -5441,58 +4595,58 @@
         <v>65535</v>
       </c>
       <c r="I40">
-        <v>86.267099999999999</v>
+        <v>83.988500000000002</v>
       </c>
       <c r="J40">
-        <v>36.769799999999996</v>
+        <v>44.860700000000001</v>
       </c>
       <c r="K40">
-        <v>2.2858900000000002</v>
+        <v>2.08771</v>
       </c>
       <c r="L40">
-        <v>26.127700000000001</v>
+        <v>17.743099999999998</v>
       </c>
       <c r="M40">
-        <v>42.364600000000003</v>
+        <v>42.024099999999997</v>
       </c>
       <c r="N40">
-        <v>265058</v>
+        <v>334073</v>
       </c>
       <c r="O40">
-        <v>360601</v>
+        <v>460883</v>
       </c>
       <c r="P40">
-        <v>73.504499999999993</v>
+        <v>72.485399999999998</v>
       </c>
       <c r="Q40">
         <v>15</v>
       </c>
       <c r="R40">
-        <v>1.5931299999999999</v>
+        <v>1.31488</v>
       </c>
       <c r="S40">
-        <v>-66.960400000000007</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T40">
-        <v>22.877800000000001</v>
+        <v>18.4998</v>
       </c>
       <c r="U40">
-        <f t="shared" si="2"/>
-        <v>90.457011877941724</v>
+        <f t="shared" si="0"/>
+        <v>83.308789047727544</v>
       </c>
       <c r="V40">
-        <v>86.267099999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22">
+        <v>83.988500000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
       <c r="A41">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B41">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D41">
         <v>1400</v>
@@ -5510,58 +4664,58 @@
         <v>65535</v>
       </c>
       <c r="I41">
-        <v>11.155099999999999</v>
+        <v>86.979299999999995</v>
       </c>
       <c r="J41">
-        <v>5.2057900000000004</v>
+        <v>31.590900000000001</v>
       </c>
       <c r="K41">
-        <v>7.9774500000000005E-3</v>
+        <v>2.8710800000000001</v>
       </c>
       <c r="L41">
-        <v>0.133329</v>
+        <v>40.094499999999996</v>
       </c>
       <c r="M41">
-        <v>9.9107299999999992</v>
+        <v>48.645699999999998</v>
       </c>
       <c r="N41">
-        <v>6206</v>
+        <v>307967</v>
       </c>
       <c r="O41">
-        <v>56413</v>
+        <v>325115</v>
       </c>
       <c r="P41">
-        <v>11.000999999999999</v>
+        <v>94.7256</v>
       </c>
       <c r="Q41">
         <v>15</v>
       </c>
       <c r="R41">
-        <v>1.07866</v>
+        <v>1.2395</v>
       </c>
       <c r="S41">
-        <v>-70.708600000000004</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T41">
-        <v>17.3354</v>
+        <v>15.864800000000001</v>
       </c>
       <c r="U41">
-        <f t="shared" si="2"/>
-        <v>11.933152897972789</v>
+        <f t="shared" si="0"/>
+        <v>83.403205987332612</v>
       </c>
       <c r="V41">
-        <v>11.155099999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22">
+        <v>86.979299999999995</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
       <c r="A42">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B42">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C42">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>1400</v>
@@ -5579,58 +4733,62 @@
         <v>65535</v>
       </c>
       <c r="I42">
-        <v>22.5413</v>
+        <v>83.590400000000002</v>
       </c>
       <c r="J42">
-        <v>10.592599999999999</v>
+        <v>53.903100000000002</v>
       </c>
       <c r="K42">
-        <v>2.6126399999999998E-3</v>
+        <v>2.4186299999999998</v>
       </c>
       <c r="L42">
-        <v>0.13994400000000001</v>
+        <v>12.433400000000001</v>
       </c>
       <c r="M42">
-        <v>10.3019</v>
+        <v>44.445500000000003</v>
       </c>
       <c r="N42">
-        <v>13189</v>
+        <v>443723</v>
       </c>
       <c r="O42">
-        <v>114836</v>
+        <v>554629</v>
       </c>
       <c r="P42">
-        <v>11.485099999999999</v>
+        <v>80.003600000000006</v>
       </c>
       <c r="Q42">
         <v>15</v>
       </c>
       <c r="R42">
-        <v>1.08134</v>
+        <v>1.3283400000000001</v>
       </c>
       <c r="S42">
-        <v>-70.708600000000004</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T42">
-        <v>17.332599999999999</v>
+        <v>36.738900000000001</v>
       </c>
       <c r="U42">
-        <f t="shared" si="2"/>
-        <v>25.587571412083058</v>
+        <f t="shared" si="0"/>
+        <v>86.344372406534674</v>
       </c>
       <c r="V42">
-        <v>22.5413</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22">
+        <v>83.590400000000002</v>
+      </c>
+      <c r="W42">
+        <f>100*(1-EXP(-(6.207*$C42 - 0.0057*$S42 + 30.9139*$A42 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
       <c r="A43">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B43">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>1400</v>
@@ -5648,58 +4806,58 @@
         <v>65535</v>
       </c>
       <c r="I43">
-        <v>34.300400000000003</v>
+        <v>85.874099999999999</v>
       </c>
       <c r="J43">
-        <v>15.9719</v>
+        <v>53.707299999999996</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>2.4706999999999999</v>
       </c>
       <c r="L43">
-        <v>0.20555100000000001</v>
+        <v>19.8218</v>
       </c>
       <c r="M43">
-        <v>13.6473</v>
+        <v>41.311399999999999</v>
       </c>
       <c r="N43">
-        <v>27366</v>
+        <v>386904</v>
       </c>
       <c r="O43">
-        <v>173157</v>
+        <v>549652</v>
       </c>
       <c r="P43">
-        <v>15.8042</v>
+        <v>70.390699999999995</v>
       </c>
       <c r="Q43">
         <v>15</v>
       </c>
       <c r="R43">
-        <v>1.0632600000000001</v>
+        <v>1.3800399999999999</v>
       </c>
       <c r="S43">
-        <v>-70.708600000000004</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T43">
-        <v>17.330200000000001</v>
+        <v>28.081099999999999</v>
       </c>
       <c r="U43">
-        <f t="shared" si="2"/>
-        <v>36.869059611258926</v>
+        <f t="shared" si="0"/>
+        <v>86.468166914490936</v>
       </c>
       <c r="V43">
-        <v>34.300400000000003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22">
+        <v>85.874099999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
       <c r="A44">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B44">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D44">
         <v>1400</v>
@@ -5717,58 +4875,58 @@
         <v>65535</v>
       </c>
       <c r="I44">
-        <v>46.510100000000001</v>
+        <v>86.286199999999994</v>
       </c>
       <c r="J44">
-        <v>21.356999999999999</v>
+        <v>49.794199999999996</v>
       </c>
       <c r="K44">
-        <v>7.7741399999999997E-3</v>
+        <v>1.24915</v>
       </c>
       <c r="L44">
-        <v>0.40173700000000001</v>
+        <v>20.2654</v>
       </c>
       <c r="M44">
-        <v>21.924299999999999</v>
+        <v>37.760599999999997</v>
       </c>
       <c r="N44">
-        <v>65023</v>
+        <v>300588</v>
       </c>
       <c r="O44">
-        <v>231556</v>
+        <v>495448</v>
       </c>
       <c r="P44">
-        <v>28.0809</v>
+        <v>60.669899999999998</v>
       </c>
       <c r="Q44">
         <v>15</v>
       </c>
       <c r="R44">
-        <v>1.02586</v>
+        <v>1.5270300000000001</v>
       </c>
       <c r="S44">
-        <v>-70.708600000000004</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T44">
-        <v>17.366599999999998</v>
+        <v>22.439</v>
       </c>
       <c r="U44">
-        <f t="shared" si="2"/>
-        <v>46.189996702547219</v>
+        <f t="shared" si="0"/>
+        <v>86.537456531090911</v>
       </c>
       <c r="V44">
-        <v>46.510100000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22">
+        <v>86.286199999999994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
       <c r="A45">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B45">
         <v>20</v>
       </c>
       <c r="C45">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="D45">
         <v>1400</v>
@@ -5786,58 +4944,58 @@
         <v>65535</v>
       </c>
       <c r="I45">
-        <v>55.146999999999998</v>
+        <v>88.121899999999997</v>
       </c>
       <c r="J45">
-        <v>26.134899999999998</v>
+        <v>43.083199999999998</v>
       </c>
       <c r="K45">
-        <v>0.13542299999999999</v>
+        <v>1.6809499999999999</v>
       </c>
       <c r="L45">
-        <v>1.18428</v>
+        <v>28.2103</v>
       </c>
       <c r="M45">
-        <v>35.926900000000003</v>
+        <v>39.0625</v>
       </c>
       <c r="N45">
-        <v>159075</v>
+        <v>279567</v>
       </c>
       <c r="O45">
-        <v>283699</v>
+        <v>436125</v>
       </c>
       <c r="P45">
-        <v>56.071800000000003</v>
+        <v>64.102500000000006</v>
       </c>
       <c r="Q45">
         <v>15</v>
       </c>
       <c r="R45">
-        <v>0.97982000000000002</v>
+        <v>1.43103</v>
       </c>
       <c r="S45">
         <v>-70.708600000000004</v>
       </c>
       <c r="T45">
-        <v>17.549299999999999</v>
+        <v>19.085899999999999</v>
       </c>
       <c r="U45">
-        <f t="shared" si="2"/>
-        <v>53.891096657258927</v>
+        <f t="shared" si="0"/>
+        <v>86.585271203899808</v>
       </c>
       <c r="V45">
-        <v>55.146999999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22">
+        <v>88.121899999999997</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23">
       <c r="A46">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B46">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C46">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="D46">
         <v>1400</v>
@@ -5855,58 +5013,58 @@
         <v>65535</v>
       </c>
       <c r="I46">
-        <v>66.2089</v>
+        <v>87.809299999999993</v>
       </c>
       <c r="J46">
-        <v>33.621200000000002</v>
+        <v>24.867799999999999</v>
       </c>
       <c r="K46">
-        <v>0.77761999999999998</v>
+        <v>3.59443</v>
       </c>
       <c r="L46">
-        <v>4.6535700000000002</v>
+        <v>36.705199999999998</v>
       </c>
       <c r="M46">
-        <v>43.9754</v>
+        <v>49.102499999999999</v>
       </c>
       <c r="N46">
-        <v>283859</v>
+        <v>246555</v>
       </c>
       <c r="O46">
-        <v>361636</v>
+        <v>255568</v>
       </c>
       <c r="P46">
-        <v>78.492999999999995</v>
+        <v>96.473299999999995</v>
       </c>
       <c r="Q46">
         <v>15</v>
       </c>
       <c r="R46">
-        <v>1.05192</v>
+        <v>1.2614700000000001</v>
       </c>
       <c r="S46">
-        <v>-70.708600000000004</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T46">
-        <v>18.141100000000002</v>
+        <v>15.8827</v>
       </c>
       <c r="U46">
-        <f t="shared" si="2"/>
-        <v>65.510876460213325</v>
+        <f t="shared" si="0"/>
+        <v>86.62160689565043</v>
       </c>
       <c r="V46">
-        <v>66.2089</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22">
+        <v>87.809299999999993</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23">
       <c r="A47">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B47">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C47">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="D47">
         <v>1400</v>
@@ -5924,58 +5082,62 @@
         <v>65535</v>
       </c>
       <c r="I47">
-        <v>77.522599999999997</v>
+        <v>88.548299999999998</v>
       </c>
       <c r="J47">
-        <v>41.662500000000001</v>
+        <v>55.014499999999998</v>
       </c>
       <c r="K47">
-        <v>1.52654</v>
+        <v>2.5572499999999998</v>
       </c>
       <c r="L47">
-        <v>12.141400000000001</v>
+        <v>15.946400000000001</v>
       </c>
       <c r="M47">
-        <v>44.040900000000001</v>
+        <v>42.023099999999999</v>
       </c>
       <c r="N47">
-        <v>343927</v>
+        <v>401780</v>
       </c>
       <c r="O47">
-        <v>436999</v>
+        <v>554314</v>
       </c>
       <c r="P47">
-        <v>78.701999999999998</v>
+        <v>72.482399999999998</v>
       </c>
       <c r="Q47">
         <v>15</v>
       </c>
       <c r="R47">
-        <v>1.21699</v>
+        <v>1.4584900000000001</v>
       </c>
       <c r="S47">
-        <v>-70.708600000000004</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T47">
-        <v>18.357700000000001</v>
+        <v>36.990600000000001</v>
       </c>
       <c r="U47">
-        <f t="shared" si="2"/>
-        <v>76.407863840012297</v>
+        <f t="shared" si="0"/>
+        <v>87.753494000257206</v>
       </c>
       <c r="V47">
-        <v>77.522599999999997</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22">
+        <v>88.548299999999998</v>
+      </c>
+      <c r="W47">
+        <f>100*(1-EXP(-(6.207*$C47 - 0.0057*$S47 + 30.9139*$A47 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C48">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="D48">
         <v>1400</v>
@@ -5993,58 +5155,58 @@
         <v>65535</v>
       </c>
       <c r="I48">
-        <v>83.988500000000002</v>
+        <v>90.224500000000006</v>
       </c>
       <c r="J48">
-        <v>44.860700000000001</v>
+        <v>43.371200000000002</v>
       </c>
       <c r="K48">
-        <v>2.08771</v>
+        <v>2.4353799999999999</v>
       </c>
       <c r="L48">
-        <v>17.743099999999998</v>
+        <v>31.7163</v>
       </c>
       <c r="M48">
-        <v>42.024099999999997</v>
+        <v>39.817500000000003</v>
       </c>
       <c r="N48">
-        <v>334073</v>
+        <v>288773</v>
       </c>
       <c r="O48">
-        <v>460883</v>
+        <v>436468</v>
       </c>
       <c r="P48">
-        <v>72.485399999999998</v>
+        <v>66.161299999999997</v>
       </c>
       <c r="Q48">
         <v>15</v>
       </c>
       <c r="R48">
-        <v>1.31488</v>
+        <v>1.4881200000000001</v>
       </c>
       <c r="S48">
-        <v>-70.708600000000004</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T48">
-        <v>18.4998</v>
+        <v>28.207899999999999</v>
       </c>
       <c r="U48">
-        <f t="shared" si="2"/>
-        <v>85.076922754012969</v>
+        <f t="shared" si="0"/>
+        <v>87.801135441510581</v>
       </c>
       <c r="V48">
-        <v>83.988500000000002</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22">
+        <v>90.224500000000006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23">
       <c r="A49">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B49">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C49">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D49">
         <v>1400</v>
@@ -6062,50 +5224,50 @@
         <v>65535</v>
       </c>
       <c r="I49">
-        <v>88.121899999999997</v>
+        <v>85.724000000000004</v>
       </c>
       <c r="J49">
-        <v>43.083199999999998</v>
+        <v>45.468299999999999</v>
       </c>
       <c r="K49">
-        <v>1.6809499999999999</v>
+        <v>1.63368</v>
       </c>
       <c r="L49">
-        <v>28.2103</v>
+        <v>22.235900000000001</v>
       </c>
       <c r="M49">
-        <v>39.0625</v>
+        <v>40.140999999999998</v>
       </c>
       <c r="N49">
-        <v>279567</v>
+        <v>302312</v>
       </c>
       <c r="O49">
-        <v>436125</v>
+        <v>450813</v>
       </c>
       <c r="P49">
-        <v>64.102500000000006</v>
+        <v>67.059299999999993</v>
       </c>
       <c r="Q49">
         <v>15</v>
       </c>
       <c r="R49">
-        <v>1.43103</v>
+        <v>1.52363</v>
       </c>
       <c r="S49">
-        <v>-70.708600000000004</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T49">
-        <v>19.085899999999999</v>
+        <v>22.544599999999999</v>
       </c>
       <c r="U49">
-        <f t="shared" si="2"/>
-        <v>88.414550302606045</v>
+        <f t="shared" si="0"/>
+        <v>87.827801060633874</v>
       </c>
       <c r="V49">
-        <v>88.121899999999997</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22">
+        <v>85.724000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
       <c r="A50">
         <v>25</v>
       </c>
@@ -6167,22 +5329,22 @@
         <v>19.157499999999999</v>
       </c>
       <c r="U50">
-        <f t="shared" si="2"/>
-        <v>89.69955225767832</v>
+        <f t="shared" si="0"/>
+        <v>87.846202199450801</v>
       </c>
       <c r="V50">
         <v>87.564400000000006</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:23">
       <c r="A51">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B51">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C51">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="D51">
         <v>1400</v>
@@ -6200,58 +5362,58 @@
         <v>65535</v>
       </c>
       <c r="I51">
-        <v>87.620800000000003</v>
+        <v>89.042900000000003</v>
       </c>
       <c r="J51">
-        <v>30.796700000000001</v>
+        <v>17.413900000000002</v>
       </c>
       <c r="K51">
-        <v>2.2576100000000001</v>
+        <v>4.92319</v>
       </c>
       <c r="L51">
-        <v>31.151399999999999</v>
+        <v>66.109300000000005</v>
       </c>
       <c r="M51">
-        <v>42.929200000000002</v>
+        <v>55.555399999999999</v>
       </c>
       <c r="N51">
-        <v>227469</v>
+        <v>229190</v>
       </c>
       <c r="O51">
-        <v>302401</v>
+        <v>183353</v>
       </c>
       <c r="P51">
-        <v>75.221000000000004</v>
+        <v>124.999</v>
       </c>
       <c r="Q51">
         <v>15</v>
       </c>
       <c r="R51">
-        <v>1.53067</v>
+        <v>1.0648</v>
       </c>
       <c r="S51">
-        <v>-70.708600000000004</v>
+        <v>-73.615899999999996</v>
       </c>
       <c r="T51">
-        <v>19.297599999999999</v>
+        <v>16.226299999999998</v>
       </c>
       <c r="U51">
-        <f t="shared" si="2"/>
-        <v>90.194283919764331</v>
+        <f t="shared" si="0"/>
+        <v>87.860185733555156</v>
       </c>
       <c r="V51">
-        <v>87.620800000000003</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22">
+        <v>89.042900000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
       <c r="A52">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B52">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="D52">
         <v>1400</v>
@@ -6269,58 +5431,62 @@
         <v>65535</v>
       </c>
       <c r="I52">
-        <v>87.615200000000002</v>
+        <v>89.776300000000006</v>
       </c>
       <c r="J52">
-        <v>24.743300000000001</v>
+        <v>48.9285</v>
       </c>
       <c r="K52">
-        <v>2.2806199999999999</v>
+        <v>2.3839899999999998</v>
       </c>
       <c r="L52">
-        <v>33.83</v>
+        <v>17.814</v>
       </c>
       <c r="M52">
-        <v>42.189300000000003</v>
+        <v>42.495800000000003</v>
       </c>
       <c r="N52">
-        <v>177190</v>
+        <v>359744</v>
       </c>
       <c r="O52">
-        <v>242798</v>
+        <v>486796</v>
       </c>
       <c r="P52">
-        <v>72.978399999999993</v>
+        <v>73.900400000000005</v>
       </c>
       <c r="Q52">
         <v>15</v>
       </c>
       <c r="R52">
-        <v>1.5173399999999999</v>
+        <v>1.5004</v>
       </c>
       <c r="S52">
-        <v>-70.708600000000004</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T52">
-        <v>19.629200000000001</v>
+        <v>36.9422</v>
       </c>
       <c r="U52">
-        <f t="shared" si="2"/>
-        <v>90.384757884807158</v>
+        <f t="shared" si="0"/>
+        <v>88.29578448417692</v>
       </c>
       <c r="V52">
-        <v>87.615200000000002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22">
+        <v>89.776300000000006</v>
+      </c>
+      <c r="W52">
+        <f>100*(1-EXP(-(6.207*$C52 - 0.0057*$S52 + 30.9139*$A52 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
       <c r="A53">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B53">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C53">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D53">
         <v>1400</v>
@@ -6338,58 +5504,58 @@
         <v>65535</v>
       </c>
       <c r="I53">
-        <v>87.388999999999996</v>
+        <v>89.726399999999998</v>
       </c>
       <c r="J53">
-        <v>28.460100000000001</v>
+        <v>47.193899999999999</v>
       </c>
       <c r="K53">
-        <v>2.3112200000000001</v>
+        <v>2.5136400000000001</v>
       </c>
       <c r="L53">
-        <v>27.2879</v>
+        <v>27.448</v>
       </c>
       <c r="M53">
-        <v>42.075600000000001</v>
+        <v>40.777000000000001</v>
       </c>
       <c r="N53">
-        <v>203041</v>
+        <v>326189</v>
       </c>
       <c r="O53">
-        <v>279521</v>
+        <v>473744</v>
       </c>
       <c r="P53">
-        <v>72.638900000000007</v>
+        <v>68.853399999999993</v>
       </c>
       <c r="Q53">
         <v>15</v>
       </c>
       <c r="R53">
-        <v>1.4970399999999999</v>
+        <v>1.4955499999999999</v>
       </c>
       <c r="S53">
-        <v>-70.708600000000004</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T53">
-        <v>19.109400000000001</v>
+        <v>28.1159</v>
       </c>
       <c r="U53">
-        <f t="shared" si="2"/>
-        <v>90.458091237287888</v>
+        <f t="shared" si="0"/>
+        <v>88.314118956054301</v>
       </c>
       <c r="V53">
-        <v>87.388999999999996</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22">
+        <v>89.726399999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
       <c r="A54">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B54">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="D54">
         <v>1400</v>
@@ -6407,58 +5573,58 @@
         <v>65535</v>
       </c>
       <c r="I54">
-        <v>11.378500000000001</v>
+        <v>85.069900000000004</v>
       </c>
       <c r="J54">
-        <v>5.2057900000000004</v>
+        <v>44.584499999999998</v>
       </c>
       <c r="K54">
-        <v>7.9774500000000005E-3</v>
+        <v>1.96347</v>
       </c>
       <c r="L54">
-        <v>0.12881300000000001</v>
+        <v>21.029599999999999</v>
       </c>
       <c r="M54">
-        <v>8.0487699999999993</v>
+        <v>41.106299999999997</v>
       </c>
       <c r="N54">
-        <v>4938</v>
+        <v>307194</v>
       </c>
       <c r="O54">
-        <v>56413</v>
+        <v>440123</v>
       </c>
       <c r="P54">
-        <v>8.7532999999999994</v>
+        <v>69.797300000000007</v>
       </c>
       <c r="Q54">
         <v>15</v>
       </c>
       <c r="R54">
-        <v>1.1269899999999999</v>
+        <v>1.5342100000000001</v>
       </c>
       <c r="S54">
-        <v>-73.615899999999996</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T54">
-        <v>14.430999999999999</v>
+        <v>22.780899999999999</v>
       </c>
       <c r="U54">
-        <f t="shared" si="2"/>
-        <v>13.336724966993261</v>
+        <f t="shared" si="0"/>
+        <v>88.324381031068143</v>
       </c>
       <c r="V54">
-        <v>11.378500000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22">
+        <v>85.069900000000004</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
       <c r="A55">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B55">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C55">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="D55">
         <v>1400</v>
@@ -6476,58 +5642,58 @@
         <v>65535</v>
       </c>
       <c r="I55">
-        <v>22.463000000000001</v>
+        <v>87.620800000000003</v>
       </c>
       <c r="J55">
-        <v>10.025600000000001</v>
+        <v>30.796700000000001</v>
       </c>
       <c r="K55">
-        <v>5.8000599999999999E-2</v>
+        <v>2.2576100000000001</v>
       </c>
       <c r="L55">
-        <v>0.19667899999999999</v>
+        <v>31.151399999999999</v>
       </c>
       <c r="M55">
-        <v>13.1676</v>
+        <v>42.929200000000002</v>
       </c>
       <c r="N55">
-        <v>16474</v>
+        <v>227469</v>
       </c>
       <c r="O55">
-        <v>108636</v>
+        <v>302401</v>
       </c>
       <c r="P55">
-        <v>15.164400000000001</v>
+        <v>75.221000000000004</v>
       </c>
       <c r="Q55">
         <v>15</v>
       </c>
       <c r="R55">
-        <v>1.10825</v>
+        <v>1.53067</v>
       </c>
       <c r="S55">
-        <v>-73.615899999999996</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T55">
-        <v>14.479799999999999</v>
+        <v>19.297599999999999</v>
       </c>
       <c r="U55">
-        <f t="shared" si="2"/>
-        <v>26.74722399758015</v>
+        <f t="shared" si="0"/>
+        <v>88.331462579259693</v>
       </c>
       <c r="V55">
-        <v>22.463000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22">
+        <v>87.620800000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
       <c r="A56">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B56">
         <v>25</v>
       </c>
       <c r="C56">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="D56">
         <v>1400</v>
@@ -6545,58 +5711,58 @@
         <v>65535</v>
       </c>
       <c r="I56">
-        <v>34.715699999999998</v>
+        <v>88.526799999999994</v>
       </c>
       <c r="J56">
-        <v>15.762600000000001</v>
+        <v>17.976600000000001</v>
       </c>
       <c r="K56">
-        <v>5.2699499999999998E-3</v>
+        <v>5.4458299999999999</v>
       </c>
       <c r="L56">
-        <v>0.22498000000000001</v>
+        <v>75.550299999999993</v>
       </c>
       <c r="M56">
-        <v>11.7529</v>
+        <v>54.7517</v>
       </c>
       <c r="N56">
-        <v>22747</v>
+        <v>230991</v>
       </c>
       <c r="O56">
-        <v>170797</v>
+        <v>190897</v>
       </c>
       <c r="P56">
-        <v>13.318099999999999</v>
+        <v>121.003</v>
       </c>
       <c r="Q56">
         <v>15</v>
       </c>
       <c r="R56">
-        <v>1.10782</v>
+        <v>1.10094</v>
       </c>
       <c r="S56">
         <v>-73.615899999999996</v>
       </c>
       <c r="T56">
-        <v>14.4993</v>
+        <v>16.788599999999999</v>
       </c>
       <c r="U56">
-        <f t="shared" si="2"/>
-        <v>37.827182210541331</v>
+        <f t="shared" si="0"/>
+        <v>88.33684404350673</v>
       </c>
       <c r="V56">
-        <v>34.715699999999998</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22">
+        <v>88.526799999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23">
       <c r="A57">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B57">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C57">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="D57">
         <v>1400</v>
@@ -6614,58 +5780,62 @@
         <v>65535</v>
       </c>
       <c r="I57">
-        <v>55.491399999999999</v>
+        <v>90.846500000000006</v>
       </c>
       <c r="J57">
-        <v>19.5532</v>
+        <v>40.3003</v>
       </c>
       <c r="K57">
-        <v>0.73683399999999999</v>
+        <v>3.0872899999999999</v>
       </c>
       <c r="L57">
-        <v>4.18133</v>
+        <v>24.270600000000002</v>
       </c>
       <c r="M57">
-        <v>50.155999999999999</v>
+        <v>43.570599999999999</v>
       </c>
       <c r="N57">
-        <v>212890</v>
+        <v>310843</v>
       </c>
       <c r="O57">
-        <v>211566</v>
+        <v>402580</v>
       </c>
       <c r="P57">
-        <v>100.626</v>
+        <v>77.212699999999998</v>
       </c>
       <c r="Q57">
         <v>15</v>
       </c>
       <c r="R57">
-        <v>0.999807</v>
+        <v>1.50186</v>
       </c>
       <c r="S57">
-        <v>-73.615899999999996</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T57">
-        <v>14.500400000000001</v>
+        <v>37.158700000000003</v>
       </c>
       <c r="U57">
-        <f t="shared" si="2"/>
-        <v>46.981612162846631</v>
+        <f t="shared" ref="U3:U66" si="1">88.64*(1-EXP(-(-0.0052*$C57 - 0.0062*$S57 + 0.2169*$A57 - 0.4879)))</f>
+        <v>88.509375297921068</v>
       </c>
       <c r="V57">
-        <v>55.491399999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22">
+        <v>90.846500000000006</v>
+      </c>
+      <c r="W57">
+        <f>100*(1-EXP(-(6.207*$C57 - 0.0057*$S57 + 30.9139*$A57 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
       <c r="A58">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B58">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C58">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="D58">
         <v>1400</v>
@@ -6683,58 +5853,58 @@
         <v>65535</v>
       </c>
       <c r="I58">
-        <v>61.714399999999998</v>
+        <v>89.557299999999998</v>
       </c>
       <c r="J58">
-        <v>26.723099999999999</v>
+        <v>50.222900000000003</v>
       </c>
       <c r="K58">
-        <v>0.29297299999999998</v>
+        <v>2.3092299999999999</v>
       </c>
       <c r="L58">
-        <v>1.96048</v>
+        <v>30.3901</v>
       </c>
       <c r="M58">
-        <v>38.727600000000002</v>
+        <v>41.006999999999998</v>
       </c>
       <c r="N58">
-        <v>183363</v>
+        <v>348784</v>
       </c>
       <c r="O58">
-        <v>290106</v>
+        <v>501763</v>
       </c>
       <c r="P58">
-        <v>63.205500000000001</v>
+        <v>69.511700000000005</v>
       </c>
       <c r="Q58">
         <v>15</v>
       </c>
       <c r="R58">
-        <v>1.0059199999999999</v>
+        <v>1.51183</v>
       </c>
       <c r="S58">
-        <v>-73.615899999999996</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T58">
-        <v>14.805899999999999</v>
+        <v>27.9954</v>
       </c>
       <c r="U58">
-        <f t="shared" si="2"/>
-        <v>54.545141387499491</v>
+        <f t="shared" si="1"/>
+        <v>88.5164881921053</v>
       </c>
       <c r="V58">
-        <v>61.714399999999998</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22">
+        <v>89.557299999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
       <c r="A59">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B59">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C59">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="D59">
         <v>1400</v>
@@ -6752,58 +5922,58 @@
         <v>65535</v>
       </c>
       <c r="I59">
-        <v>67.334000000000003</v>
+        <v>86.011600000000001</v>
       </c>
       <c r="J59">
-        <v>27.108000000000001</v>
+        <v>37.925800000000002</v>
       </c>
       <c r="K59">
-        <v>1.58396</v>
+        <v>2.3621400000000001</v>
       </c>
       <c r="L59">
-        <v>14.362399999999999</v>
+        <v>28.040199999999999</v>
       </c>
       <c r="M59">
-        <v>46.2849</v>
+        <v>42.6</v>
       </c>
       <c r="N59">
-        <v>246957</v>
+        <v>277500</v>
       </c>
       <c r="O59">
-        <v>286602</v>
+        <v>373909</v>
       </c>
       <c r="P59">
-        <v>86.167199999999994</v>
+        <v>74.215900000000005</v>
       </c>
       <c r="Q59">
         <v>15</v>
       </c>
       <c r="R59">
-        <v>1.19346</v>
+        <v>1.5398799999999999</v>
       </c>
       <c r="S59">
-        <v>-73.615899999999996</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T59">
-        <v>14.797000000000001</v>
+        <v>23.2805</v>
       </c>
       <c r="U59">
-        <f t="shared" si="2"/>
-        <v>65.95734803856439</v>
+        <f t="shared" si="1"/>
+        <v>88.520468011471479</v>
       </c>
       <c r="V59">
-        <v>67.334000000000003</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22">
+        <v>86.011600000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
       <c r="A60">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="B60">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C60">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="D60">
         <v>1400</v>
@@ -6821,58 +5991,58 @@
         <v>65535</v>
       </c>
       <c r="I60">
-        <v>79.526300000000006</v>
+        <v>87.615200000000002</v>
       </c>
       <c r="J60">
-        <v>33.062600000000003</v>
+        <v>24.743300000000001</v>
       </c>
       <c r="K60">
-        <v>1.8160000000000001</v>
+        <v>2.2806199999999999</v>
       </c>
       <c r="L60">
-        <v>21.401700000000002</v>
+        <v>33.83</v>
       </c>
       <c r="M60">
-        <v>47.088999999999999</v>
+        <v>42.189300000000003</v>
       </c>
       <c r="N60">
-        <v>308208</v>
+        <v>177190</v>
       </c>
       <c r="O60">
-        <v>346314</v>
+        <v>242798</v>
       </c>
       <c r="P60">
-        <v>88.996700000000004</v>
+        <v>72.978399999999993</v>
       </c>
       <c r="Q60">
         <v>15</v>
       </c>
       <c r="R60">
-        <v>1.20096</v>
+        <v>1.5173399999999999</v>
       </c>
       <c r="S60">
-        <v>-73.615899999999996</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T60">
-        <v>15.4857</v>
+        <v>19.629200000000001</v>
       </c>
       <c r="U60">
-        <f t="shared" si="2"/>
-        <v>76.659674068933171</v>
+        <f t="shared" si="1"/>
+        <v>88.523213768555053</v>
       </c>
       <c r="V60">
-        <v>79.526300000000006</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22">
+        <v>87.615200000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23">
       <c r="A61">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B61">
         <v>25</v>
       </c>
       <c r="C61">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="D61">
         <v>1400</v>
@@ -6890,58 +6060,58 @@
         <v>65535</v>
       </c>
       <c r="I61">
-        <v>86.979299999999995</v>
+        <v>89.659300000000002</v>
       </c>
       <c r="J61">
-        <v>31.590900000000001</v>
+        <v>16.953700000000001</v>
       </c>
       <c r="K61">
-        <v>2.8710800000000001</v>
+        <v>5.3432399999999998</v>
       </c>
       <c r="L61">
-        <v>40.094499999999996</v>
+        <v>81.020099999999999</v>
       </c>
       <c r="M61">
-        <v>48.645699999999998</v>
+        <v>54.936</v>
       </c>
       <c r="N61">
-        <v>307967</v>
+        <v>219660</v>
       </c>
       <c r="O61">
-        <v>325115</v>
+        <v>180187</v>
       </c>
       <c r="P61">
-        <v>94.7256</v>
+        <v>121.907</v>
       </c>
       <c r="Q61">
         <v>15</v>
       </c>
       <c r="R61">
-        <v>1.2395</v>
+        <v>1.0932500000000001</v>
       </c>
       <c r="S61">
         <v>-73.615899999999996</v>
       </c>
       <c r="T61">
-        <v>15.864800000000001</v>
+        <v>16.3247</v>
       </c>
       <c r="U61">
-        <f t="shared" si="2"/>
-        <v>85.17387085015595</v>
+        <f t="shared" si="1"/>
+        <v>88.525300011717079</v>
       </c>
       <c r="V61">
-        <v>86.979299999999995</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22">
+        <v>89.659300000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23">
       <c r="A62">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B62">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D62">
         <v>1400</v>
@@ -6959,58 +6129,62 @@
         <v>65535</v>
       </c>
       <c r="I62">
-        <v>87.809299999999993</v>
+        <v>90.504400000000004</v>
       </c>
       <c r="J62">
-        <v>24.867799999999999</v>
+        <v>42.448599999999999</v>
       </c>
       <c r="K62">
-        <v>3.59443</v>
+        <v>3.0270700000000001</v>
       </c>
       <c r="L62">
-        <v>36.705199999999998</v>
+        <v>23.2728</v>
       </c>
       <c r="M62">
-        <v>49.102499999999999</v>
+        <v>43.3795</v>
       </c>
       <c r="N62">
-        <v>246555</v>
+        <v>323369</v>
       </c>
       <c r="O62">
-        <v>255568</v>
+        <v>422073</v>
       </c>
       <c r="P62">
-        <v>96.473299999999995</v>
+        <v>76.614500000000007</v>
       </c>
       <c r="Q62">
         <v>15</v>
       </c>
       <c r="R62">
-        <v>1.2614700000000001</v>
+        <v>1.5224200000000001</v>
       </c>
       <c r="S62">
-        <v>-73.615899999999996</v>
+        <v>-52.646799999999999</v>
       </c>
       <c r="T62">
-        <v>15.8827</v>
+        <v>37.303800000000003</v>
       </c>
       <c r="U62">
-        <f t="shared" si="2"/>
-        <v>88.451875765459675</v>
+        <f t="shared" si="1"/>
+        <v>88.58970888899124</v>
       </c>
       <c r="V62">
-        <v>87.809299999999993</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22">
+        <v>90.504400000000004</v>
+      </c>
+      <c r="W62">
+        <f>100*(1-EXP(-(6.207*$C62 - 0.0057*$S62 + 30.9139*$A62 - 0.3386)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23">
       <c r="A63">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B63">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="D63">
         <v>1400</v>
@@ -7028,58 +6202,58 @@
         <v>65535</v>
       </c>
       <c r="I63">
-        <v>89.042900000000003</v>
+        <v>89.909599999999998</v>
       </c>
       <c r="J63">
-        <v>17.413900000000002</v>
+        <v>48.381300000000003</v>
       </c>
       <c r="K63">
-        <v>4.92319</v>
+        <v>3.0191400000000002</v>
       </c>
       <c r="L63">
-        <v>66.109300000000005</v>
+        <v>28.368600000000001</v>
       </c>
       <c r="M63">
-        <v>55.555399999999999</v>
+        <v>41.976300000000002</v>
       </c>
       <c r="N63">
-        <v>229190</v>
+        <v>350465</v>
       </c>
       <c r="O63">
-        <v>183353</v>
+        <v>484446</v>
       </c>
       <c r="P63">
-        <v>124.999</v>
+        <v>72.343500000000006</v>
       </c>
       <c r="Q63">
         <v>15</v>
       </c>
       <c r="R63">
-        <v>1.0648</v>
+        <v>1.5185900000000001</v>
       </c>
       <c r="S63">
-        <v>-73.615899999999996</v>
+        <v>-61.677700000000002</v>
       </c>
       <c r="T63">
-        <v>16.226299999999998</v>
+        <v>28.028300000000002</v>
       </c>
       <c r="U63">
-        <f t="shared" si="2"/>
-        <v>89.713922732526868</v>
+        <f t="shared" si="1"/>
+        <v>88.592447385962487</v>
       </c>
       <c r="V63">
-        <v>89.042900000000003</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22">
+        <v>89.909599999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
       <c r="A64">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B64">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C64">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="D64">
         <v>1400</v>
@@ -7097,58 +6271,58 @@
         <v>65535</v>
       </c>
       <c r="I64">
-        <v>88.526799999999994</v>
+        <v>86.267099999999999</v>
       </c>
       <c r="J64">
-        <v>17.976600000000001</v>
+        <v>36.769799999999996</v>
       </c>
       <c r="K64">
-        <v>5.4458299999999999</v>
+        <v>2.2858900000000002</v>
       </c>
       <c r="L64">
-        <v>75.550299999999993</v>
+        <v>26.127700000000001</v>
       </c>
       <c r="M64">
-        <v>54.7517</v>
+        <v>42.364600000000003</v>
       </c>
       <c r="N64">
-        <v>230991</v>
+        <v>265058</v>
       </c>
       <c r="O64">
-        <v>190897</v>
+        <v>360601</v>
       </c>
       <c r="P64">
-        <v>121.003</v>
+        <v>73.504499999999993</v>
       </c>
       <c r="Q64">
         <v>15</v>
       </c>
       <c r="R64">
-        <v>1.10094</v>
+        <v>1.5931299999999999</v>
       </c>
       <c r="S64">
-        <v>-73.615899999999996</v>
+        <v>-66.960400000000007</v>
       </c>
       <c r="T64">
-        <v>16.788599999999999</v>
+        <v>22.877800000000001</v>
       </c>
       <c r="U64">
-        <f t="shared" si="2"/>
-        <v>90.199816618667029</v>
+        <f t="shared" si="1"/>
+        <v>88.593979634720611</v>
       </c>
       <c r="V64">
-        <v>88.526799999999994</v>
+        <v>86.267099999999999</v>
       </c>
     </row>
     <row r="65" spans="1:22">
       <c r="A65">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B65">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C65">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="D65">
         <v>1400</v>
@@ -7166,47 +6340,47 @@
         <v>65535</v>
       </c>
       <c r="I65">
-        <v>89.659300000000002</v>
+        <v>87.388999999999996</v>
       </c>
       <c r="J65">
-        <v>16.953700000000001</v>
+        <v>28.460100000000001</v>
       </c>
       <c r="K65">
-        <v>5.3432399999999998</v>
+        <v>2.3112200000000001</v>
       </c>
       <c r="L65">
-        <v>81.020099999999999</v>
+        <v>27.2879</v>
       </c>
       <c r="M65">
-        <v>54.936</v>
+        <v>42.075600000000001</v>
       </c>
       <c r="N65">
-        <v>219660</v>
+        <v>203041</v>
       </c>
       <c r="O65">
-        <v>180187</v>
+        <v>279521</v>
       </c>
       <c r="P65">
-        <v>121.907</v>
+        <v>72.638900000000007</v>
       </c>
       <c r="Q65">
         <v>15</v>
       </c>
       <c r="R65">
-        <v>1.0932500000000001</v>
+        <v>1.4970399999999999</v>
       </c>
       <c r="S65">
-        <v>-73.615899999999996</v>
+        <v>-70.708600000000004</v>
       </c>
       <c r="T65">
-        <v>16.3247</v>
+        <v>19.109400000000001</v>
       </c>
       <c r="U65">
-        <f t="shared" si="2"/>
-        <v>90.38688799932811</v>
+        <f t="shared" si="1"/>
+        <v>88.59503676382478</v>
       </c>
       <c r="V65">
-        <v>89.659300000000002</v>
+        <v>87.388999999999996</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -7271,14 +6445,17 @@
         <v>15.8339</v>
       </c>
       <c r="U66">
-        <f t="shared" si="2"/>
-        <v>90.4589113411743</v>
+        <f t="shared" si="1"/>
+        <v>88.595839977036249</v>
       </c>
       <c r="V66">
         <v>87.439599999999999</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W66">
+    <sortCondition ref="A2:A66"/>
+  </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
